--- a/research/traditional_assets/database/data/philippines/philippines_transportation.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_transportation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_lbc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0694</v>
+        <v>0.02975</v>
       </c>
       <c r="G2">
-        <v>-0.7224264705882353</v>
+        <v>0.05549302289723228</v>
       </c>
       <c r="H2">
-        <v>-0.7224264705882353</v>
+        <v>0.05549302289723228</v>
       </c>
       <c r="I2">
-        <v>-0.6084558823529411</v>
+        <v>0.01834476910030067</v>
       </c>
       <c r="J2">
-        <v>-0.6084558823529411</v>
+        <v>0.0137585768252255</v>
       </c>
       <c r="K2">
-        <v>-2.68</v>
+        <v>-1.922</v>
       </c>
       <c r="L2">
-        <v>-0.4926470588235294</v>
+        <v>-0.007408835093670495</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.001340789222850607</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.3293444328824142</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.001340789222850607</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.3293444328824142</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>1.21</v>
+        <v>32.521</v>
       </c>
       <c r="V2">
-        <v>0.3288043478260869</v>
+        <v>0.06888437016796933</v>
       </c>
       <c r="W2">
-        <v>-1.288461538461539</v>
+        <v>0.06416911683574456</v>
       </c>
       <c r="X2">
-        <v>0.2040630333334911</v>
+        <v>0.1538727704259888</v>
       </c>
       <c r="Y2">
-        <v>-1.49252457179503</v>
+        <v>-0.08970365359024424</v>
       </c>
       <c r="Z2">
-        <v>0.6543180178012991</v>
+        <v>2.83677240866494</v>
       </c>
       <c r="AA2">
-        <v>-0.3981236468607169</v>
+        <v>0.01062650803087967</v>
       </c>
       <c r="AB2">
-        <v>0.117774609433641</v>
+        <v>0.09924030168824627</v>
       </c>
       <c r="AC2">
-        <v>-0.5158982562943579</v>
+        <v>-0.0886137936573666</v>
       </c>
       <c r="AD2">
-        <v>5.65</v>
+        <v>109.79</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.65</v>
+        <v>109.79</v>
       </c>
       <c r="AG2">
-        <v>4.44</v>
+        <v>77.26899999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6055734190782422</v>
+        <v>0.1886750300738959</v>
       </c>
       <c r="AI2">
-        <v>0.9701236263736263</v>
+        <v>0.7551101818481939</v>
       </c>
       <c r="AJ2">
-        <v>0.5467980295566502</v>
+        <v>0.1406478951689089</v>
       </c>
       <c r="AK2">
-        <v>0.9622886866059818</v>
+        <v>0.6845537098560354</v>
       </c>
       <c r="AL2">
-        <v>0.045</v>
+        <v>9.588999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.043</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="AN2">
-        <v>-1.765625</v>
+        <v>-28.16572601334018</v>
       </c>
       <c r="AO2">
-        <v>-73.55555555555556</v>
+        <v>0.4962978412764627</v>
       </c>
       <c r="AP2">
-        <v>-1.3875</v>
+        <v>-19.8227296049256</v>
       </c>
       <c r="AQ2">
-        <v>-76.97674418604652</v>
+        <v>0.511060996563574</v>
       </c>
     </row>
     <row r="3">
@@ -707,124 +712,9016 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>LBC Express Holdings, Inc. (PSE:LBC)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0418</v>
+      </c>
+      <c r="G3">
+        <v>0.05463836477987422</v>
+      </c>
+      <c r="H3">
+        <v>0.05463836477987422</v>
+      </c>
+      <c r="I3">
+        <v>0.01878930817610063</v>
+      </c>
+      <c r="J3">
+        <v>0.009394654088050314</v>
+      </c>
+      <c r="K3">
+        <v>-1.76</v>
+      </c>
+      <c r="L3">
+        <v>-0.006918238993710692</v>
+      </c>
+      <c r="M3">
+        <v>0.633</v>
+      </c>
+      <c r="N3">
+        <v>0.001348242811501597</v>
+      </c>
+      <c r="O3">
+        <v>-0.3596590909090909</v>
+      </c>
+      <c r="P3">
+        <v>0.633</v>
+      </c>
+      <c r="Q3">
+        <v>0.001348242811501597</v>
+      </c>
+      <c r="R3">
+        <v>-0.3596590909090909</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>31.7</v>
+      </c>
+      <c r="V3">
+        <v>0.06751863684771033</v>
+      </c>
+      <c r="W3">
+        <v>-0.05146198830409356</v>
+      </c>
+      <c r="X3">
+        <v>0.1094110324809955</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1608730207850891</v>
+      </c>
+      <c r="Z3">
+        <v>2.893868729382323</v>
+      </c>
+      <c r="AA3">
+        <v>0.02718689568877261</v>
+      </c>
+      <c r="AB3">
+        <v>0.09930005597466467</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07211316028589206</v>
+      </c>
+      <c r="AD3">
+        <v>104.1</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>104.1</v>
+      </c>
+      <c r="AG3">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="AH3">
+        <v>0.1814853556485355</v>
+      </c>
+      <c r="AI3">
+        <v>0.7451682176091625</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1336039859752722</v>
+      </c>
+      <c r="AK3">
+        <v>0.6703703703703703</v>
+      </c>
+      <c r="AL3">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="AM3">
+        <v>9.265999999999998</v>
+      </c>
+      <c r="AN3">
+        <v>-25.96009975062344</v>
+      </c>
+      <c r="AO3">
+        <v>0.5010482180293502</v>
+      </c>
+      <c r="AP3">
+        <v>-18.05486284289277</v>
+      </c>
+      <c r="AQ3">
+        <v>0.5158644506799052</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Metro Alliance Holdings &amp; Equities Corp. (PSE:MAH)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0177</v>
+      </c>
+      <c r="G4">
+        <v>0.09880478087649402</v>
+      </c>
+      <c r="H4">
+        <v>0.09880478087649402</v>
+      </c>
+      <c r="I4">
+        <v>-0.004183266932270917</v>
+      </c>
+      <c r="J4">
+        <v>-0.004183266932270917</v>
+      </c>
+      <c r="K4">
+        <v>-0.162</v>
+      </c>
+      <c r="L4">
+        <v>-0.03227091633466136</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.821</v>
+      </c>
+      <c r="V4">
+        <v>0.3145593869731801</v>
+      </c>
+      <c r="W4">
+        <v>0.1798002219755827</v>
+      </c>
+      <c r="X4">
+        <v>0.1983345083709821</v>
+      </c>
+      <c r="Y4">
+        <v>-0.01853428639539945</v>
+      </c>
+      <c r="Z4">
+        <v>1.418479796552698</v>
+      </c>
+      <c r="AA4">
+        <v>-0.00593387962701328</v>
+      </c>
+      <c r="AB4">
+        <v>0.09918054740182788</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1051144270288412</v>
+      </c>
+      <c r="AD4">
+        <v>5.69</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>5.69</v>
+      </c>
+      <c r="AG4">
+        <v>4.869000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.6855421686746987</v>
+      </c>
+      <c r="AI4">
+        <v>0.9989466292134831</v>
+      </c>
+      <c r="AJ4">
+        <v>0.6510228640192539</v>
+      </c>
+      <c r="AK4">
+        <v>0.9987692307692307</v>
+      </c>
+      <c r="AL4">
+        <v>0.049</v>
+      </c>
+      <c r="AM4">
+        <v>0.046</v>
+      </c>
+      <c r="AN4">
+        <v>50.80357142857143</v>
+      </c>
+      <c r="AO4">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="AP4">
+        <v>43.47321428571429</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.4565217391304348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LBC Express Holdings, Inc. (PSE:LBC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:LBC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.70020964360587</v>
+      </c>
+      <c r="F2">
+        <v>-6.82846278502383</v>
+      </c>
+      <c r="G2">
+        <v>-25.9600997506234</v>
+      </c>
+      <c r="H2">
+        <v>-1.43042394014963</v>
+      </c>
+      <c r="I2">
+        <v>0.181485355648536</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>469.5</v>
+      </c>
+      <c r="L2">
+        <v>510.567414603748</v>
+      </c>
+      <c r="M2">
+        <v>541.9</v>
+      </c>
+      <c r="N2">
+        <v>484.603414603748</v>
+      </c>
+      <c r="O2">
+        <v>104.1</v>
+      </c>
+      <c r="P2">
+        <v>5.736</v>
+      </c>
+      <c r="Q2">
+        <v>0.09930005597466469</v>
+      </c>
+      <c r="R2">
+        <v>0.106453217754313</v>
+      </c>
+      <c r="S2">
+        <v>0.0536986777832879</v>
+      </c>
+      <c r="T2">
+        <v>0.6464592282659229</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.109411032480995</v>
+      </c>
+      <c r="X2">
+        <v>0.100998611587529</v>
+      </c>
+      <c r="Y2">
+        <v>0.95618603152805</v>
+      </c>
+      <c r="Z2">
+        <v>0.842268431585964</v>
+      </c>
+      <c r="AA2">
+        <v>104.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.07159823704438384</v>
+      </c>
+      <c r="AC2">
+        <v>-0.70020964360587</v>
+      </c>
+      <c r="AD2">
+        <v>104.1</v>
+      </c>
+      <c r="AE2">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>2.67</v>
+      </c>
+      <c r="AG2">
+        <v>-4.01</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>469.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>14.991</v>
+      </c>
+      <c r="AR2">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>104.1</v>
+      </c>
+      <c r="AT2">
+        <v>31.7</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-104.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>31.7</v>
+      </c>
+      <c r="H2">
+        <v>469.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K2">
+        <v>2.67</v>
+      </c>
+      <c r="L2">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="O2">
+        <v>-2.338333333333333</v>
+      </c>
+      <c r="P2">
+        <v>-7.015000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>-4.345000000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1064532177543126</v>
+      </c>
+      <c r="C3">
+        <v>510.567414603748</v>
+      </c>
       <c r="D3">
-        <v>0.0694</v>
+        <v>484.603414603748</v>
+      </c>
+      <c r="E3">
+        <v>-98.36399999999999</v>
+      </c>
+      <c r="F3">
+        <v>5.736000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.7224264705882353</v>
+        <v>31.7</v>
       </c>
       <c r="H3">
-        <v>-0.7224264705882353</v>
+        <v>469.5</v>
       </c>
       <c r="I3">
-        <v>-0.6084558823529411</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.6084558823529411</v>
+        <v>-6.683333333333334</v>
       </c>
       <c r="K3">
-        <v>-2.68</v>
+        <v>2.67</v>
       </c>
       <c r="L3">
-        <v>-0.4926470588235294</v>
+        <v>-9.353333333333333</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.3697568</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>-10.72309013333333</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-2.680772533333333</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>-8.042317600000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>-5.372317600000001</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1009986115875286</v>
+      </c>
+      <c r="T3">
+        <v>0.842268431585964</v>
       </c>
       <c r="U3">
-        <v>1.21</v>
+        <v>0.2388</v>
       </c>
       <c r="V3">
-        <v>0.3288043478260869</v>
+        <v>-1.707115696255958</v>
       </c>
       <c r="W3">
-        <v>-1.288461538461539</v>
-      </c>
-      <c r="X3">
-        <v>0.2040630333334911</v>
+        <v>0.6464592282659227</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-1.49252457179503</v>
+        <v>-6.828462785023832</v>
       </c>
       <c r="Z3">
-        <v>0.6543180178012991</v>
-      </c>
-      <c r="AA3">
-        <v>-0.3981236468607169</v>
-      </c>
-      <c r="AB3">
-        <v>0.117774609433641</v>
-      </c>
-      <c r="AC3">
-        <v>-0.5158982562943579</v>
-      </c>
-      <c r="AD3">
-        <v>5.65</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>5.65</v>
-      </c>
-      <c r="AG3">
-        <v>4.44</v>
-      </c>
-      <c r="AH3">
-        <v>0.6055734190782422</v>
-      </c>
-      <c r="AI3">
-        <v>0.9701236263736263</v>
-      </c>
-      <c r="AJ3">
-        <v>0.5467980295566502</v>
-      </c>
-      <c r="AK3">
-        <v>0.9622886866059818</v>
-      </c>
-      <c r="AL3">
-        <v>0.045</v>
-      </c>
-      <c r="AM3">
-        <v>0.043</v>
-      </c>
-      <c r="AN3">
-        <v>-1.765625</v>
-      </c>
-      <c r="AO3">
-        <v>-73.55555555555556</v>
-      </c>
-      <c r="AP3">
-        <v>-1.3875</v>
-      </c>
-      <c r="AQ3">
-        <v>-76.97674418604652</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1084532177543126</v>
+      </c>
+      <c r="C4">
+        <v>490.9166686601196</v>
+      </c>
+      <c r="D4">
+        <v>470.6886686601196</v>
+      </c>
+      <c r="E4">
+        <v>-92.62799999999999</v>
+      </c>
+      <c r="F4">
+        <v>11.472</v>
+      </c>
+      <c r="G4">
+        <v>31.7</v>
+      </c>
+      <c r="H4">
+        <v>469.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K4">
+        <v>2.67</v>
+      </c>
+      <c r="L4">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M4">
+        <v>2.7395136</v>
+      </c>
+      <c r="N4">
+        <v>-12.09284693333333</v>
+      </c>
+      <c r="O4">
+        <v>-3.023211733333333</v>
+      </c>
+      <c r="P4">
+        <v>-9.0696352</v>
+      </c>
+      <c r="Q4">
+        <v>-6.399635200000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1016332912976055</v>
+      </c>
+      <c r="T4">
+        <v>0.8508630074184738</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-0.853557848127979</v>
+      </c>
+      <c r="W4">
+        <v>0.4426296141329614</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-3.414231392511916</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1104532177543126</v>
+      </c>
+      <c r="C5">
+        <v>472.0427054698539</v>
+      </c>
+      <c r="D5">
+        <v>457.5507054698539</v>
+      </c>
+      <c r="E5">
+        <v>-86.892</v>
+      </c>
+      <c r="F5">
+        <v>17.208</v>
+      </c>
+      <c r="G5">
+        <v>31.7</v>
+      </c>
+      <c r="H5">
+        <v>469.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K5">
+        <v>2.67</v>
+      </c>
+      <c r="L5">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M5">
+        <v>4.1092704</v>
+      </c>
+      <c r="N5">
+        <v>-13.46260373333333</v>
+      </c>
+      <c r="O5">
+        <v>-3.365650933333333</v>
+      </c>
+      <c r="P5">
+        <v>-10.0969528</v>
+      </c>
+      <c r="Q5">
+        <v>-7.4269528</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1022810571872715</v>
+      </c>
+      <c r="T5">
+        <v>0.8596347910001075</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.5690385654186528</v>
+      </c>
+      <c r="W5">
+        <v>0.3746864094219743</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-2.276154261674611</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1124532177543126</v>
+      </c>
+      <c r="C6">
+        <v>453.8822461068938</v>
+      </c>
+      <c r="D6">
+        <v>445.1262461068939</v>
+      </c>
+      <c r="E6">
+        <v>-81.15599999999999</v>
+      </c>
+      <c r="F6">
+        <v>22.944</v>
+      </c>
+      <c r="G6">
+        <v>31.7</v>
+      </c>
+      <c r="H6">
+        <v>469.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K6">
+        <v>2.67</v>
+      </c>
+      <c r="L6">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M6">
+        <v>5.479027200000001</v>
+      </c>
+      <c r="N6">
+        <v>-14.83236053333333</v>
+      </c>
+      <c r="O6">
+        <v>-3.708090133333334</v>
+      </c>
+      <c r="P6">
+        <v>-11.1242704</v>
+      </c>
+      <c r="Q6">
+        <v>-8.4542704</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1029423181996389</v>
+      </c>
+      <c r="T6">
+        <v>0.8685893200730254</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.4267789240639895</v>
+      </c>
+      <c r="W6">
+        <v>0.3407148070664807</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-1.707115696255958</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1144532177543126</v>
+      </c>
+      <c r="C7">
+        <v>436.3787031174479</v>
+      </c>
+      <c r="D7">
+        <v>433.3587031174479</v>
+      </c>
+      <c r="E7">
+        <v>-75.41999999999999</v>
+      </c>
+      <c r="F7">
+        <v>28.68</v>
+      </c>
+      <c r="G7">
+        <v>31.7</v>
+      </c>
+      <c r="H7">
+        <v>469.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K7">
+        <v>2.67</v>
+      </c>
+      <c r="L7">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M7">
+        <v>6.848784000000001</v>
+      </c>
+      <c r="N7">
+        <v>-16.20211733333333</v>
+      </c>
+      <c r="O7">
+        <v>-4.050529333333333</v>
+      </c>
+      <c r="P7">
+        <v>-12.151588</v>
+      </c>
+      <c r="Q7">
+        <v>-9.481588</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1036175004964772</v>
+      </c>
+      <c r="T7">
+        <v>0.8777323655474784</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.3414231392511916</v>
+      </c>
+      <c r="W7">
+        <v>0.3203318456531846</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.365692557004766</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1164532177543126</v>
+      </c>
+      <c r="C8">
+        <v>419.4813188078227</v>
+      </c>
+      <c r="D8">
+        <v>422.1973188078227</v>
+      </c>
+      <c r="E8">
+        <v>-69.684</v>
+      </c>
+      <c r="F8">
+        <v>34.416</v>
+      </c>
+      <c r="G8">
+        <v>31.7</v>
+      </c>
+      <c r="H8">
+        <v>469.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K8">
+        <v>2.67</v>
+      </c>
+      <c r="L8">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M8">
+        <v>8.2185408</v>
+      </c>
+      <c r="N8">
+        <v>-17.57187413333333</v>
+      </c>
+      <c r="O8">
+        <v>-4.392968533333333</v>
+      </c>
+      <c r="P8">
+        <v>-13.1789056</v>
+      </c>
+      <c r="Q8">
+        <v>-10.5089056</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1043070483740993</v>
+      </c>
+      <c r="T8">
+        <v>0.8870699439043663</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.2845192827093264</v>
+      </c>
+      <c r="W8">
+        <v>0.3067432047109871</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-1.138077130837305</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1184532177543126</v>
+      </c>
+      <c r="C9">
+        <v>403.1444333518182</v>
+      </c>
+      <c r="D9">
+        <v>411.5964333518182</v>
+      </c>
+      <c r="E9">
+        <v>-63.94799999999999</v>
+      </c>
+      <c r="F9">
+        <v>40.15200000000001</v>
+      </c>
+      <c r="G9">
+        <v>31.7</v>
+      </c>
+      <c r="H9">
+        <v>469.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K9">
+        <v>2.67</v>
+      </c>
+      <c r="L9">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M9">
+        <v>9.588297600000002</v>
+      </c>
+      <c r="N9">
+        <v>-18.94163093333334</v>
+      </c>
+      <c r="O9">
+        <v>-4.735407733333334</v>
+      </c>
+      <c r="P9">
+        <v>-14.2062232</v>
+      </c>
+      <c r="Q9">
+        <v>-11.5362232</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1050114252383369</v>
+      </c>
+      <c r="T9">
+        <v>0.8966083303979617</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.2438736708937083</v>
+      </c>
+      <c r="W9">
+        <v>0.2970370326094176</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-0.975494683574833</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1204532177543126</v>
+      </c>
+      <c r="C10">
+        <v>387.3268604592403</v>
+      </c>
+      <c r="D10">
+        <v>401.5148604592403</v>
+      </c>
+      <c r="E10">
+        <v>-58.21199999999999</v>
+      </c>
+      <c r="F10">
+        <v>45.88800000000001</v>
+      </c>
+      <c r="G10">
+        <v>31.7</v>
+      </c>
+      <c r="H10">
+        <v>469.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K10">
+        <v>2.67</v>
+      </c>
+      <c r="L10">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M10">
+        <v>10.9580544</v>
+      </c>
+      <c r="N10">
+        <v>-20.31138773333333</v>
+      </c>
+      <c r="O10">
+        <v>-5.077846933333333</v>
+      </c>
+      <c r="P10">
+        <v>-15.2335408</v>
+      </c>
+      <c r="Q10">
+        <v>-12.5635408</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1057311146431015</v>
+      </c>
+      <c r="T10">
+        <v>0.9063540731196786</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.2133894620319947</v>
+      </c>
+      <c r="W10">
+        <v>0.2897574035332404</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-0.8535578481279789</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1224532177543126</v>
+      </c>
+      <c r="C11">
+        <v>371.9913526043607</v>
+      </c>
+      <c r="D11">
+        <v>391.9153526043607</v>
+      </c>
+      <c r="E11">
+        <v>-52.47599999999999</v>
+      </c>
+      <c r="F11">
+        <v>51.624</v>
+      </c>
+      <c r="G11">
+        <v>31.7</v>
+      </c>
+      <c r="H11">
+        <v>469.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K11">
+        <v>2.67</v>
+      </c>
+      <c r="L11">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M11">
+        <v>12.3278112</v>
+      </c>
+      <c r="N11">
+        <v>-21.68114453333333</v>
+      </c>
+      <c r="O11">
+        <v>-5.420286133333334</v>
+      </c>
+      <c r="P11">
+        <v>-16.2608584</v>
+      </c>
+      <c r="Q11">
+        <v>-13.5908584</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1064666213974213</v>
+      </c>
+      <c r="T11">
+        <v>0.9163140079891257</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.1896795218062176</v>
+      </c>
+      <c r="W11">
+        <v>0.2840954698073248</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.7587180872248702</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1244532177543126</v>
+      </c>
+      <c r="C12">
+        <v>357.1041411757712</v>
+      </c>
+      <c r="D12">
+        <v>382.7641411757713</v>
+      </c>
+      <c r="E12">
+        <v>-46.73999999999999</v>
+      </c>
+      <c r="F12">
+        <v>57.36000000000001</v>
+      </c>
+      <c r="G12">
+        <v>31.7</v>
+      </c>
+      <c r="H12">
+        <v>469.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K12">
+        <v>2.67</v>
+      </c>
+      <c r="L12">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M12">
+        <v>13.697568</v>
+      </c>
+      <c r="N12">
+        <v>-23.05090133333334</v>
+      </c>
+      <c r="O12">
+        <v>-5.762725333333334</v>
+      </c>
+      <c r="P12">
+        <v>-17.288176</v>
+      </c>
+      <c r="Q12">
+        <v>-14.618176</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1072184727462815</v>
+      </c>
+      <c r="T12">
+        <v>0.9264952747445604</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.1707115696255958</v>
+      </c>
+      <c r="W12">
+        <v>0.2795659228265923</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.6828462785023832</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1264532177543126</v>
+      </c>
+      <c r="C13">
+        <v>342.6345395811638</v>
+      </c>
+      <c r="D13">
+        <v>374.0305395811639</v>
+      </c>
+      <c r="E13">
+        <v>-41.00399999999999</v>
+      </c>
+      <c r="F13">
+        <v>63.096</v>
+      </c>
+      <c r="G13">
+        <v>31.7</v>
+      </c>
+      <c r="H13">
+        <v>469.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K13">
+        <v>2.67</v>
+      </c>
+      <c r="L13">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M13">
+        <v>15.0673248</v>
+      </c>
+      <c r="N13">
+        <v>-24.42065813333333</v>
+      </c>
+      <c r="O13">
+        <v>-6.105164533333333</v>
+      </c>
+      <c r="P13">
+        <v>-18.3154936</v>
+      </c>
+      <c r="Q13">
+        <v>-15.6454936</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1079872196310712</v>
+      </c>
+      <c r="T13">
+        <v>0.9369053340113531</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1551923360232689</v>
+      </c>
+      <c r="W13">
+        <v>0.2758599298423566</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.6207693440930755</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1284532177543126</v>
+      </c>
+      <c r="C14">
+        <v>328.5545994761658</v>
+      </c>
+      <c r="D14">
+        <v>365.6865994761658</v>
+      </c>
+      <c r="E14">
+        <v>-35.268</v>
+      </c>
+      <c r="F14">
+        <v>68.83199999999999</v>
+      </c>
+      <c r="G14">
+        <v>31.7</v>
+      </c>
+      <c r="H14">
+        <v>469.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K14">
+        <v>2.67</v>
+      </c>
+      <c r="L14">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M14">
+        <v>16.4370816</v>
+      </c>
+      <c r="N14">
+        <v>-25.79041493333333</v>
+      </c>
+      <c r="O14">
+        <v>-6.447603733333333</v>
+      </c>
+      <c r="P14">
+        <v>-19.3428112</v>
+      </c>
+      <c r="Q14">
+        <v>-16.6728112</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1087734380359697</v>
+      </c>
+      <c r="T14">
+        <v>0.9475519855342094</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1422596413546632</v>
+      </c>
+      <c r="W14">
+        <v>0.2727716023554936</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.5690385654186527</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1304532177543126</v>
+      </c>
+      <c r="C15">
+        <v>314.8388120025511</v>
+      </c>
+      <c r="D15">
+        <v>357.7068120025511</v>
+      </c>
+      <c r="E15">
+        <v>-29.53199999999998</v>
+      </c>
+      <c r="F15">
+        <v>74.56800000000001</v>
+      </c>
+      <c r="G15">
+        <v>31.7</v>
+      </c>
+      <c r="H15">
+        <v>469.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K15">
+        <v>2.67</v>
+      </c>
+      <c r="L15">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M15">
+        <v>17.8068384</v>
+      </c>
+      <c r="N15">
+        <v>-27.16017173333334</v>
+      </c>
+      <c r="O15">
+        <v>-6.790042933333334</v>
+      </c>
+      <c r="P15">
+        <v>-20.3701288</v>
+      </c>
+      <c r="Q15">
+        <v>-17.7001288</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1095777304271878</v>
+      </c>
+      <c r="T15">
+        <v>0.9584433876667866</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1313165920196891</v>
+      </c>
+      <c r="W15">
+        <v>0.2701584021743018</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.5252663680787562</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1324532177543126</v>
+      </c>
+      <c r="C16">
+        <v>301.4638473074789</v>
+      </c>
+      <c r="D16">
+        <v>350.0678473074789</v>
+      </c>
+      <c r="E16">
+        <v>-23.79599999999998</v>
+      </c>
+      <c r="F16">
+        <v>80.30400000000002</v>
+      </c>
+      <c r="G16">
+        <v>31.7</v>
+      </c>
+      <c r="H16">
+        <v>469.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K16">
+        <v>2.67</v>
+      </c>
+      <c r="L16">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M16">
+        <v>19.1765952</v>
+      </c>
+      <c r="N16">
+        <v>-28.52992853333334</v>
+      </c>
+      <c r="O16">
+        <v>-7.132482133333335</v>
+      </c>
+      <c r="P16">
+        <v>-21.39744640000001</v>
+      </c>
+      <c r="Q16">
+        <v>-18.72744640000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1104007272926202</v>
+      </c>
+      <c r="T16">
+        <v>0.9695880782210515</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1219368354468541</v>
+      </c>
+      <c r="W16">
+        <v>0.2679185163047088</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.4877473417874165</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1344532177543126</v>
+      </c>
+      <c r="C17">
+        <v>288.4083267408707</v>
+      </c>
+      <c r="D17">
+        <v>342.7483267408707</v>
+      </c>
+      <c r="E17">
+        <v>-18.05999999999999</v>
+      </c>
+      <c r="F17">
+        <v>86.04000000000001</v>
+      </c>
+      <c r="G17">
+        <v>31.7</v>
+      </c>
+      <c r="H17">
+        <v>469.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K17">
+        <v>2.67</v>
+      </c>
+      <c r="L17">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M17">
+        <v>20.546352</v>
+      </c>
+      <c r="N17">
+        <v>-29.89968533333334</v>
+      </c>
+      <c r="O17">
+        <v>-7.474921333333334</v>
+      </c>
+      <c r="P17">
+        <v>-22.424764</v>
+      </c>
+      <c r="Q17">
+        <v>-19.754764</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1112430887901804</v>
+      </c>
+      <c r="T17">
+        <v>0.980994996788358</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.1138077130837305</v>
+      </c>
+      <c r="W17">
+        <v>0.2659772818843948</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.4552308523349222</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1364532177543126</v>
+      </c>
+      <c r="C18">
+        <v>275.6526230460432</v>
+      </c>
+      <c r="D18">
+        <v>335.7286230460432</v>
+      </c>
+      <c r="E18">
+        <v>-12.32399999999998</v>
+      </c>
+      <c r="F18">
+        <v>91.77600000000001</v>
+      </c>
+      <c r="G18">
+        <v>31.7</v>
+      </c>
+      <c r="H18">
+        <v>469.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K18">
+        <v>2.67</v>
+      </c>
+      <c r="L18">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M18">
+        <v>21.9161088</v>
+      </c>
+      <c r="N18">
+        <v>-31.26944213333334</v>
+      </c>
+      <c r="O18">
+        <v>-7.817360533333334</v>
+      </c>
+      <c r="P18">
+        <v>-23.4520816</v>
+      </c>
+      <c r="Q18">
+        <v>-20.7820816</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.112105506513873</v>
+      </c>
+      <c r="T18">
+        <v>0.9926735086548862</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.1066947310159974</v>
+      </c>
+      <c r="W18">
+        <v>0.2642787017666202</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.4267789240639894</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1384532177543126</v>
+      </c>
+      <c r="C19">
+        <v>263.1786846109039</v>
+      </c>
+      <c r="D19">
+        <v>328.9906846109039</v>
+      </c>
+      <c r="E19">
+        <v>-6.58799999999998</v>
+      </c>
+      <c r="F19">
+        <v>97.51200000000001</v>
+      </c>
+      <c r="G19">
+        <v>31.7</v>
+      </c>
+      <c r="H19">
+        <v>469.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K19">
+        <v>2.67</v>
+      </c>
+      <c r="L19">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M19">
+        <v>23.2858656</v>
+      </c>
+      <c r="N19">
+        <v>-32.63919893333334</v>
+      </c>
+      <c r="O19">
+        <v>-8.159799733333335</v>
+      </c>
+      <c r="P19">
+        <v>-24.4793992</v>
+      </c>
+      <c r="Q19">
+        <v>-21.8093992</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1129887053875342</v>
+      </c>
+      <c r="T19">
+        <v>1.004633430445909</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.1004185703679975</v>
+      </c>
+      <c r="W19">
+        <v>0.2627799546038778</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.4016742814719902</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1404532177543126</v>
+      </c>
+      <c r="C20">
+        <v>250.969880466011</v>
+      </c>
+      <c r="D20">
+        <v>322.517880466011</v>
+      </c>
+      <c r="E20">
+        <v>-0.8519999999999897</v>
+      </c>
+      <c r="F20">
+        <v>103.248</v>
+      </c>
+      <c r="G20">
+        <v>31.7</v>
+      </c>
+      <c r="H20">
+        <v>469.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K20">
+        <v>2.67</v>
+      </c>
+      <c r="L20">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M20">
+        <v>24.6556224</v>
+      </c>
+      <c r="N20">
+        <v>-34.00895573333334</v>
+      </c>
+      <c r="O20">
+        <v>-8.502238933333334</v>
+      </c>
+      <c r="P20">
+        <v>-25.5067168</v>
+      </c>
+      <c r="Q20">
+        <v>-22.8367168</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1138934456971382</v>
+      </c>
+      <c r="T20">
+        <v>1.016885057646469</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.09483976090310878</v>
+      </c>
+      <c r="W20">
+        <v>0.2614477349036624</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.3793590436124352</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1424532177543126</v>
+      </c>
+      <c r="C21">
+        <v>239.010863227309</v>
+      </c>
+      <c r="D21">
+        <v>316.2948632273091</v>
+      </c>
+      <c r="E21">
+        <v>4.884000000000015</v>
+      </c>
+      <c r="F21">
+        <v>108.984</v>
+      </c>
+      <c r="G21">
+        <v>31.7</v>
+      </c>
+      <c r="H21">
+        <v>469.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K21">
+        <v>2.67</v>
+      </c>
+      <c r="L21">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M21">
+        <v>26.0253792</v>
+      </c>
+      <c r="N21">
+        <v>-35.37871253333333</v>
+      </c>
+      <c r="O21">
+        <v>-8.844678133333334</v>
+      </c>
+      <c r="P21">
+        <v>-26.5340344</v>
+      </c>
+      <c r="Q21">
+        <v>-23.8640344</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1148205252736461</v>
+      </c>
+      <c r="T21">
+        <v>1.029439194160622</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.08984819453978726</v>
+      </c>
+      <c r="W21">
+        <v>0.2602557488561012</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.3593927781591491</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1444532177543126</v>
+      </c>
+      <c r="C22">
+        <v>227.2874476057077</v>
+      </c>
+      <c r="D22">
+        <v>310.3074476057077</v>
+      </c>
+      <c r="E22">
+        <v>10.62000000000002</v>
+      </c>
+      <c r="F22">
+        <v>114.72</v>
+      </c>
+      <c r="G22">
+        <v>31.7</v>
+      </c>
+      <c r="H22">
+        <v>469.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K22">
+        <v>2.67</v>
+      </c>
+      <c r="L22">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M22">
+        <v>27.395136</v>
+      </c>
+      <c r="N22">
+        <v>-36.74846933333334</v>
+      </c>
+      <c r="O22">
+        <v>-9.187117333333335</v>
+      </c>
+      <c r="P22">
+        <v>-27.56135200000001</v>
+      </c>
+      <c r="Q22">
+        <v>-24.891352</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1157707818395667</v>
+      </c>
+      <c r="T22">
+        <v>1.04230718408763</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.0853557848127979</v>
+      </c>
+      <c r="W22">
+        <v>0.2591829614132962</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.3414231392511917</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1464532177543126</v>
+      </c>
+      <c r="C23">
+        <v>215.7865024590815</v>
+      </c>
+      <c r="D23">
+        <v>304.5425024590816</v>
+      </c>
+      <c r="E23">
+        <v>16.35600000000001</v>
+      </c>
+      <c r="F23">
+        <v>120.456</v>
+      </c>
+      <c r="G23">
+        <v>31.7</v>
+      </c>
+      <c r="H23">
+        <v>469.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K23">
+        <v>2.67</v>
+      </c>
+      <c r="L23">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M23">
+        <v>28.7648928</v>
+      </c>
+      <c r="N23">
+        <v>-38.11822613333334</v>
+      </c>
+      <c r="O23">
+        <v>-9.529556533333334</v>
+      </c>
+      <c r="P23">
+        <v>-28.5886696</v>
+      </c>
+      <c r="Q23">
+        <v>-25.9186696</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1167450955337384</v>
+      </c>
+      <c r="T23">
+        <v>1.055500945911525</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.0812912236312361</v>
+      </c>
+      <c r="W23">
+        <v>0.2582123442031392</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.3251648945249446</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1484532177543126</v>
+      </c>
+      <c r="C24">
+        <v>204.4958546576566</v>
+      </c>
+      <c r="D24">
+        <v>298.9878546576566</v>
+      </c>
+      <c r="E24">
+        <v>22.09200000000001</v>
+      </c>
+      <c r="F24">
+        <v>126.192</v>
+      </c>
+      <c r="G24">
+        <v>31.7</v>
+      </c>
+      <c r="H24">
+        <v>469.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K24">
+        <v>2.67</v>
+      </c>
+      <c r="L24">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M24">
+        <v>30.1346496</v>
+      </c>
+      <c r="N24">
+        <v>-39.48798293333333</v>
+      </c>
+      <c r="O24">
+        <v>-9.871995733333334</v>
+      </c>
+      <c r="P24">
+        <v>-29.6159872</v>
+      </c>
+      <c r="Q24">
+        <v>-26.9459872</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1177443916303248</v>
+      </c>
+      <c r="T24">
+        <v>1.069033009320647</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.07759616801163446</v>
+      </c>
+      <c r="W24">
+        <v>0.2573299649211783</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.3103846720465377</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1504532177543126</v>
+      </c>
+      <c r="C25">
+        <v>193.4042032815258</v>
+      </c>
+      <c r="D25">
+        <v>293.6322032815258</v>
+      </c>
+      <c r="E25">
+        <v>27.828</v>
+      </c>
+      <c r="F25">
+        <v>131.928</v>
+      </c>
+      <c r="G25">
+        <v>31.7</v>
+      </c>
+      <c r="H25">
+        <v>469.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K25">
+        <v>2.67</v>
+      </c>
+      <c r="L25">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M25">
+        <v>31.5044064</v>
+      </c>
+      <c r="N25">
+        <v>-40.85773973333333</v>
+      </c>
+      <c r="O25">
+        <v>-10.21443493333333</v>
+      </c>
+      <c r="P25">
+        <v>-30.6433048</v>
+      </c>
+      <c r="Q25">
+        <v>-27.9733048</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1187696434696797</v>
+      </c>
+      <c r="T25">
+        <v>1.082916554896239</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.07422242157634601</v>
+      </c>
+      <c r="W25">
+        <v>0.2565243142724314</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.296889686305384</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1524532177543126</v>
+      </c>
+      <c r="C26">
+        <v>182.501042877563</v>
+      </c>
+      <c r="D26">
+        <v>288.465042877563</v>
+      </c>
+      <c r="E26">
+        <v>33.56399999999999</v>
+      </c>
+      <c r="F26">
+        <v>137.664</v>
+      </c>
+      <c r="G26">
+        <v>31.7</v>
+      </c>
+      <c r="H26">
+        <v>469.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K26">
+        <v>2.67</v>
+      </c>
+      <c r="L26">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M26">
+        <v>32.8741632</v>
+      </c>
+      <c r="N26">
+        <v>-42.22749653333333</v>
+      </c>
+      <c r="O26">
+        <v>-10.55687413333333</v>
+      </c>
+      <c r="P26">
+        <v>-31.6706224</v>
+      </c>
+      <c r="Q26">
+        <v>-29.0006224</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1198218756205965</v>
+      </c>
+      <c r="T26">
+        <v>1.097165456934348</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.0711298206773316</v>
+      </c>
+      <c r="W26">
+        <v>0.2557858011777468</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.2845192827093264</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1544532177543126</v>
+      </c>
+      <c r="C27">
+        <v>171.7765946790812</v>
+      </c>
+      <c r="D27">
+        <v>283.4765946790812</v>
+      </c>
+      <c r="E27">
+        <v>39.30000000000001</v>
+      </c>
+      <c r="F27">
+        <v>143.4</v>
+      </c>
+      <c r="G27">
+        <v>31.7</v>
+      </c>
+      <c r="H27">
+        <v>469.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K27">
+        <v>2.67</v>
+      </c>
+      <c r="L27">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M27">
+        <v>34.24392</v>
+      </c>
+      <c r="N27">
+        <v>-43.59725333333333</v>
+      </c>
+      <c r="O27">
+        <v>-10.89931333333333</v>
+      </c>
+      <c r="P27">
+        <v>-32.69794</v>
+      </c>
+      <c r="Q27">
+        <v>-30.02794</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1209021672955378</v>
+      </c>
+      <c r="T27">
+        <v>1.111794329693472</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.06828462785023832</v>
+      </c>
+      <c r="W27">
+        <v>0.2551063691306369</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.2731385114009532</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1564532177543126</v>
+      </c>
+      <c r="C28">
+        <v>161.2217448407189</v>
+      </c>
+      <c r="D28">
+        <v>278.657744840719</v>
+      </c>
+      <c r="E28">
+        <v>45.03600000000003</v>
+      </c>
+      <c r="F28">
+        <v>149.136</v>
+      </c>
+      <c r="G28">
+        <v>31.7</v>
+      </c>
+      <c r="H28">
+        <v>469.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K28">
+        <v>2.67</v>
+      </c>
+      <c r="L28">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M28">
+        <v>35.61367680000001</v>
+      </c>
+      <c r="N28">
+        <v>-44.96701013333334</v>
+      </c>
+      <c r="O28">
+        <v>-11.24175253333333</v>
+      </c>
+      <c r="P28">
+        <v>-33.72525760000001</v>
+      </c>
+      <c r="Q28">
+        <v>-31.0552576</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1220116560427748</v>
+      </c>
+      <c r="T28">
+        <v>1.126818577392033</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.06565829600984453</v>
+      </c>
+      <c r="W28">
+        <v>0.2544792010871509</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.2626331840393781</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1584532177543126</v>
+      </c>
+      <c r="C29">
+        <v>150.8279888677388</v>
+      </c>
+      <c r="D29">
+        <v>273.9999888677388</v>
+      </c>
+      <c r="E29">
+        <v>50.77200000000002</v>
+      </c>
+      <c r="F29">
+        <v>154.872</v>
+      </c>
+      <c r="G29">
+        <v>31.7</v>
+      </c>
+      <c r="H29">
+        <v>469.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K29">
+        <v>2.67</v>
+      </c>
+      <c r="L29">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M29">
+        <v>36.98343360000001</v>
+      </c>
+      <c r="N29">
+        <v>-46.33676693333334</v>
+      </c>
+      <c r="O29">
+        <v>-11.58419173333333</v>
+      </c>
+      <c r="P29">
+        <v>-34.7525752</v>
+      </c>
+      <c r="Q29">
+        <v>-32.0825752</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1231515417419909</v>
+      </c>
+      <c r="T29">
+        <v>1.142254448315212</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.06322650726873918</v>
+      </c>
+      <c r="W29">
+        <v>0.253898489935775</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.2529060290749567</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1604532177543126</v>
+      </c>
+      <c r="C30">
+        <v>140.5873815268775</v>
+      </c>
+      <c r="D30">
+        <v>269.4953815268775</v>
+      </c>
+      <c r="E30">
+        <v>56.50800000000004</v>
+      </c>
+      <c r="F30">
+        <v>160.608</v>
+      </c>
+      <c r="G30">
+        <v>31.7</v>
+      </c>
+      <c r="H30">
+        <v>469.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K30">
+        <v>2.67</v>
+      </c>
+      <c r="L30">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M30">
+        <v>38.35319040000001</v>
+      </c>
+      <c r="N30">
+        <v>-47.70652373333334</v>
+      </c>
+      <c r="O30">
+        <v>-11.92663093333334</v>
+      </c>
+      <c r="P30">
+        <v>-35.77989280000001</v>
+      </c>
+      <c r="Q30">
+        <v>-33.1098928</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1243230909328519</v>
+      </c>
+      <c r="T30">
+        <v>1.158119093430701</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.06096841772342707</v>
+      </c>
+      <c r="W30">
+        <v>0.2533592581523544</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.2438736708937081</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1624532177543126</v>
+      </c>
+      <c r="C31">
+        <v>130.4924916181274</v>
+      </c>
+      <c r="D31">
+        <v>265.1364916181274</v>
+      </c>
+      <c r="E31">
+        <v>62.244</v>
+      </c>
+      <c r="F31">
+        <v>166.344</v>
+      </c>
+      <c r="G31">
+        <v>31.7</v>
+      </c>
+      <c r="H31">
+        <v>469.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K31">
+        <v>2.67</v>
+      </c>
+      <c r="L31">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M31">
+        <v>39.7229472</v>
+      </c>
+      <c r="N31">
+        <v>-49.07628053333333</v>
+      </c>
+      <c r="O31">
+        <v>-12.26907013333333</v>
+      </c>
+      <c r="P31">
+        <v>-36.8072104</v>
+      </c>
+      <c r="Q31">
+        <v>-34.1372104</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1255276415093709</v>
+      </c>
+      <c r="T31">
+        <v>1.174430629957893</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.05886605849158476</v>
+      </c>
+      <c r="W31">
+        <v>0.2528572147677904</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.2354642339663391</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1644532177543126</v>
+      </c>
+      <c r="C32">
+        <v>120.5363610658554</v>
+      </c>
+      <c r="D32">
+        <v>260.9163610658554</v>
+      </c>
+      <c r="E32">
+        <v>67.98000000000002</v>
+      </c>
+      <c r="F32">
+        <v>172.08</v>
+      </c>
+      <c r="G32">
+        <v>31.7</v>
+      </c>
+      <c r="H32">
+        <v>469.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K32">
+        <v>2.67</v>
+      </c>
+      <c r="L32">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M32">
+        <v>41.092704</v>
+      </c>
+      <c r="N32">
+        <v>-50.44603733333334</v>
+      </c>
+      <c r="O32">
+        <v>-12.61150933333333</v>
+      </c>
+      <c r="P32">
+        <v>-37.83452800000001</v>
+      </c>
+      <c r="Q32">
+        <v>-35.164528</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1267666078166477</v>
+      </c>
+      <c r="T32">
+        <v>1.191208210385863</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.05690385654186527</v>
+      </c>
+      <c r="W32">
+        <v>0.2523886409421975</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.227615426167461</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1664532177543126</v>
+      </c>
+      <c r="C33">
+        <v>110.7124678555483</v>
+      </c>
+      <c r="D33">
+        <v>256.8284678555484</v>
+      </c>
+      <c r="E33">
+        <v>73.71600000000001</v>
+      </c>
+      <c r="F33">
+        <v>177.816</v>
+      </c>
+      <c r="G33">
+        <v>31.7</v>
+      </c>
+      <c r="H33">
+        <v>469.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K33">
+        <v>2.67</v>
+      </c>
+      <c r="L33">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M33">
+        <v>42.4624608</v>
+      </c>
+      <c r="N33">
+        <v>-51.81579413333333</v>
+      </c>
+      <c r="O33">
+        <v>-12.95394853333333</v>
+      </c>
+      <c r="P33">
+        <v>-38.8618456</v>
+      </c>
+      <c r="Q33">
+        <v>-36.1918456</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.128041486190802</v>
+      </c>
+      <c r="T33">
+        <v>1.208472097492905</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.05506824826632123</v>
+      </c>
+      <c r="W33">
+        <v>0.2519502976859975</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.2202729930652849</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1684532177543126</v>
+      </c>
+      <c r="C34">
+        <v>101.0146924009317</v>
+      </c>
+      <c r="D34">
+        <v>252.8666924009317</v>
+      </c>
+      <c r="E34">
+        <v>79.45200000000003</v>
+      </c>
+      <c r="F34">
+        <v>183.552</v>
+      </c>
+      <c r="G34">
+        <v>31.7</v>
+      </c>
+      <c r="H34">
+        <v>469.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K34">
+        <v>2.67</v>
+      </c>
+      <c r="L34">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M34">
+        <v>43.83221760000001</v>
+      </c>
+      <c r="N34">
+        <v>-53.18555093333334</v>
+      </c>
+      <c r="O34">
+        <v>-13.29638773333333</v>
+      </c>
+      <c r="P34">
+        <v>-39.88916320000001</v>
+      </c>
+      <c r="Q34">
+        <v>-37.2191632</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1293538609877255</v>
+      </c>
+      <c r="T34">
+        <v>1.226243745985448</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.05334736550799869</v>
+      </c>
+      <c r="W34">
+        <v>0.2515393508833101</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.2133894620319947</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1704532177543126</v>
+      </c>
+      <c r="C35">
+        <v>91.43728697667802</v>
+      </c>
+      <c r="D35">
+        <v>249.025286976678</v>
+      </c>
+      <c r="E35">
+        <v>85.18800000000002</v>
+      </c>
+      <c r="F35">
+        <v>189.288</v>
+      </c>
+      <c r="G35">
+        <v>31.7</v>
+      </c>
+      <c r="H35">
+        <v>469.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K35">
+        <v>2.67</v>
+      </c>
+      <c r="L35">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M35">
+        <v>45.2019744</v>
+      </c>
+      <c r="N35">
+        <v>-54.55530773333334</v>
+      </c>
+      <c r="O35">
+        <v>-13.63882693333333</v>
+      </c>
+      <c r="P35">
+        <v>-40.9164808</v>
+      </c>
+      <c r="Q35">
+        <v>-38.2464808</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1307054111517214</v>
+      </c>
+      <c r="T35">
+        <v>1.244545891447917</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.05173077867442297</v>
+      </c>
+      <c r="W35">
+        <v>0.2511533099474522</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.2069231146976918</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1724532177543126</v>
+      </c>
+      <c r="C36">
+        <v>81.97484789558607</v>
+      </c>
+      <c r="D36">
+        <v>245.2988478955861</v>
+      </c>
+      <c r="E36">
+        <v>90.92400000000004</v>
+      </c>
+      <c r="F36">
+        <v>195.024</v>
+      </c>
+      <c r="G36">
+        <v>31.7</v>
+      </c>
+      <c r="H36">
+        <v>469.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K36">
+        <v>2.67</v>
+      </c>
+      <c r="L36">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M36">
+        <v>46.57173120000001</v>
+      </c>
+      <c r="N36">
+        <v>-55.92506453333334</v>
+      </c>
+      <c r="O36">
+        <v>-13.98126613333334</v>
+      </c>
+      <c r="P36">
+        <v>-41.94379840000001</v>
+      </c>
+      <c r="Q36">
+        <v>-39.2737984</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.132097917381293</v>
+      </c>
+      <c r="T36">
+        <v>1.263402647378946</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.05020928518399876</v>
+      </c>
+      <c r="W36">
+        <v>0.2507899773019389</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.200837140735995</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1744532177543126</v>
+      </c>
+      <c r="C37">
+        <v>72.62229014699139</v>
+      </c>
+      <c r="D37">
+        <v>241.6822901469914</v>
+      </c>
+      <c r="E37">
+        <v>96.66000000000003</v>
+      </c>
+      <c r="F37">
+        <v>200.76</v>
+      </c>
+      <c r="G37">
+        <v>31.7</v>
+      </c>
+      <c r="H37">
+        <v>469.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K37">
+        <v>2.67</v>
+      </c>
+      <c r="L37">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M37">
+        <v>47.94148800000001</v>
+      </c>
+      <c r="N37">
+        <v>-57.29482133333334</v>
+      </c>
+      <c r="O37">
+        <v>-14.32370533333333</v>
+      </c>
+      <c r="P37">
+        <v>-42.971116</v>
+      </c>
+      <c r="Q37">
+        <v>-40.301116</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1335332699563898</v>
+      </c>
+      <c r="T37">
+        <v>1.282839611184776</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.04877473417874166</v>
+      </c>
+      <c r="W37">
+        <v>0.2504474065218835</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.1950989367149667</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1764532177543126</v>
+      </c>
+      <c r="C38">
+        <v>63.3748242460874</v>
+      </c>
+      <c r="D38">
+        <v>238.1708242460874</v>
+      </c>
+      <c r="E38">
+        <v>102.396</v>
+      </c>
+      <c r="F38">
+        <v>206.496</v>
+      </c>
+      <c r="G38">
+        <v>31.7</v>
+      </c>
+      <c r="H38">
+        <v>469.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K38">
+        <v>2.67</v>
+      </c>
+      <c r="L38">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M38">
+        <v>49.3112448</v>
+      </c>
+      <c r="N38">
+        <v>-58.66457813333334</v>
+      </c>
+      <c r="O38">
+        <v>-14.66614453333333</v>
+      </c>
+      <c r="P38">
+        <v>-43.9984336</v>
+      </c>
+      <c r="Q38">
+        <v>-41.3284336</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1350134772994584</v>
+      </c>
+      <c r="T38">
+        <v>1.302883980109538</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.04741988045155439</v>
+      </c>
+      <c r="W38">
+        <v>0.2501238674518312</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.1896795218062175</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1784532177543126</v>
+      </c>
+      <c r="C39">
+        <v>54.22793507251899</v>
+      </c>
+      <c r="D39">
+        <v>234.759935072519</v>
+      </c>
+      <c r="E39">
+        <v>108.132</v>
+      </c>
+      <c r="F39">
+        <v>212.232</v>
+      </c>
+      <c r="G39">
+        <v>31.7</v>
+      </c>
+      <c r="H39">
+        <v>469.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K39">
+        <v>2.67</v>
+      </c>
+      <c r="L39">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M39">
+        <v>50.6810016</v>
+      </c>
+      <c r="N39">
+        <v>-60.03433493333333</v>
+      </c>
+      <c r="O39">
+        <v>-15.00858373333333</v>
+      </c>
+      <c r="P39">
+        <v>-45.0257512</v>
+      </c>
+      <c r="Q39">
+        <v>-42.3557512</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1365406753518307</v>
+      </c>
+      <c r="T39">
+        <v>1.323564678206515</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.04613826206097184</v>
+      </c>
+      <c r="W39">
+        <v>0.2498178169801601</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.1845530482438873</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1804532177543126</v>
+      </c>
+      <c r="C40">
+        <v>45.17736250164108</v>
+      </c>
+      <c r="D40">
+        <v>231.4453625016411</v>
+      </c>
+      <c r="E40">
+        <v>113.868</v>
+      </c>
+      <c r="F40">
+        <v>217.968</v>
+      </c>
+      <c r="G40">
+        <v>31.7</v>
+      </c>
+      <c r="H40">
+        <v>469.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K40">
+        <v>2.67</v>
+      </c>
+      <c r="L40">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M40">
+        <v>52.05075840000001</v>
+      </c>
+      <c r="N40">
+        <v>-61.40409173333334</v>
+      </c>
+      <c r="O40">
+        <v>-15.35102293333333</v>
+      </c>
+      <c r="P40">
+        <v>-46.05306880000001</v>
+      </c>
+      <c r="Q40">
+        <v>-43.3830688</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1381171378575054</v>
+      </c>
+      <c r="T40">
+        <v>1.344912495596943</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.04492409726989363</v>
+      </c>
+      <c r="W40">
+        <v>0.2495278744280506</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.1796963890795744</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1824532177543126</v>
+      </c>
+      <c r="C41">
+        <v>36.21908365373559</v>
+      </c>
+      <c r="D41">
+        <v>228.2230836537356</v>
+      </c>
+      <c r="E41">
+        <v>119.604</v>
+      </c>
+      <c r="F41">
+        <v>223.704</v>
+      </c>
+      <c r="G41">
+        <v>31.7</v>
+      </c>
+      <c r="H41">
+        <v>469.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K41">
+        <v>2.67</v>
+      </c>
+      <c r="L41">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M41">
+        <v>53.4205152</v>
+      </c>
+      <c r="N41">
+        <v>-62.77384853333334</v>
+      </c>
+      <c r="O41">
+        <v>-15.69346213333333</v>
+      </c>
+      <c r="P41">
+        <v>-47.0803864</v>
+      </c>
+      <c r="Q41">
+        <v>-44.4103864</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1397452876584481</v>
+      </c>
+      <c r="T41">
+        <v>1.366960241426401</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.04377219733989636</v>
+      </c>
+      <c r="W41">
+        <v>0.2492528007247673</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.1750887893595854</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1844532177543126</v>
+      </c>
+      <c r="C42">
+        <v>27.3492966056705</v>
+      </c>
+      <c r="D42">
+        <v>225.0892966056705</v>
+      </c>
+      <c r="E42">
+        <v>125.34</v>
+      </c>
+      <c r="F42">
+        <v>229.44</v>
+      </c>
+      <c r="G42">
+        <v>31.7</v>
+      </c>
+      <c r="H42">
+        <v>469.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K42">
+        <v>2.67</v>
+      </c>
+      <c r="L42">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M42">
+        <v>54.79027200000001</v>
+      </c>
+      <c r="N42">
+        <v>-64.14360533333334</v>
+      </c>
+      <c r="O42">
+        <v>-16.03590133333334</v>
+      </c>
+      <c r="P42">
+        <v>-48.10770400000001</v>
+      </c>
+      <c r="Q42">
+        <v>-45.437704</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1414277091194223</v>
+      </c>
+      <c r="T42">
+        <v>1.389742912116841</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.04267789240639895</v>
+      </c>
+      <c r="W42">
+        <v>0.2489914807066481</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.1707115696255959</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1864532177543126</v>
+      </c>
+      <c r="C43">
+        <v>18.56440542633689</v>
+      </c>
+      <c r="D43">
+        <v>222.0404054263369</v>
+      </c>
+      <c r="E43">
+        <v>131.076</v>
+      </c>
+      <c r="F43">
+        <v>235.176</v>
+      </c>
+      <c r="G43">
+        <v>31.7</v>
+      </c>
+      <c r="H43">
+        <v>469.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K43">
+        <v>2.67</v>
+      </c>
+      <c r="L43">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M43">
+        <v>56.16002880000001</v>
+      </c>
+      <c r="N43">
+        <v>-65.51336213333335</v>
+      </c>
+      <c r="O43">
+        <v>-16.37834053333334</v>
+      </c>
+      <c r="P43">
+        <v>-49.13502160000001</v>
+      </c>
+      <c r="Q43">
+        <v>-46.46502160000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1431671618163616</v>
+      </c>
+      <c r="T43">
+        <v>1.413297876728991</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.04163696820136483</v>
+      </c>
+      <c r="W43">
+        <v>0.2487429080064859</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.1665478728054595</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1884532177543126</v>
+      </c>
+      <c r="C44">
+        <v>9.861006412025603</v>
+      </c>
+      <c r="D44">
+        <v>219.0730064120256</v>
+      </c>
+      <c r="E44">
+        <v>136.812</v>
+      </c>
+      <c r="F44">
+        <v>240.912</v>
+      </c>
+      <c r="G44">
+        <v>31.7</v>
+      </c>
+      <c r="H44">
+        <v>469.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K44">
+        <v>2.67</v>
+      </c>
+      <c r="L44">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M44">
+        <v>57.5297856</v>
+      </c>
+      <c r="N44">
+        <v>-66.88311893333334</v>
+      </c>
+      <c r="O44">
+        <v>-16.72077973333333</v>
+      </c>
+      <c r="P44">
+        <v>-50.16233920000001</v>
+      </c>
+      <c r="Q44">
+        <v>-47.4923392</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1449665956407816</v>
+      </c>
+      <c r="T44">
+        <v>1.43766508150018</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.04064561181561805</v>
+      </c>
+      <c r="W44">
+        <v>0.2485061721015696</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.1625824472624722</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1904532177543126</v>
+      </c>
+      <c r="C45">
+        <v>1.235875410968447</v>
+      </c>
+      <c r="D45">
+        <v>216.1838754109685</v>
+      </c>
+      <c r="E45">
+        <v>142.548</v>
+      </c>
+      <c r="F45">
+        <v>246.648</v>
+      </c>
+      <c r="G45">
+        <v>31.7</v>
+      </c>
+      <c r="H45">
+        <v>469.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K45">
+        <v>2.67</v>
+      </c>
+      <c r="L45">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M45">
+        <v>58.8995424</v>
+      </c>
+      <c r="N45">
+        <v>-68.25287573333334</v>
+      </c>
+      <c r="O45">
+        <v>-17.06321893333334</v>
+      </c>
+      <c r="P45">
+        <v>-51.18965680000001</v>
+      </c>
+      <c r="Q45">
+        <v>-48.51965680000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1468291674941287</v>
+      </c>
+      <c r="T45">
+        <v>1.462887275912464</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.03970036502920833</v>
+      </c>
+      <c r="W45">
+        <v>0.2482804471689749</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.1588014601168335</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1924532177543126</v>
+      </c>
+      <c r="C46">
+        <v>-7.314043862191795</v>
+      </c>
+      <c r="D46">
+        <v>213.3699561378082</v>
+      </c>
+      <c r="E46">
+        <v>148.284</v>
+      </c>
+      <c r="F46">
+        <v>252.384</v>
+      </c>
+      <c r="G46">
+        <v>31.7</v>
+      </c>
+      <c r="H46">
+        <v>469.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K46">
+        <v>2.67</v>
+      </c>
+      <c r="L46">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M46">
+        <v>60.26929920000001</v>
+      </c>
+      <c r="N46">
+        <v>-69.62263253333334</v>
+      </c>
+      <c r="O46">
+        <v>-17.40565813333334</v>
+      </c>
+      <c r="P46">
+        <v>-52.21697440000001</v>
+      </c>
+      <c r="Q46">
+        <v>-49.54697440000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1487582597708096</v>
+      </c>
+      <c r="T46">
+        <v>1.489010262982329</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.03879808400581723</v>
+      </c>
+      <c r="W46">
+        <v>0.2480649824605892</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.155192336023269</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1944532177543126</v>
+      </c>
+      <c r="C47">
+        <v>-15.79165061104285</v>
+      </c>
+      <c r="D47">
+        <v>210.6283493889572</v>
+      </c>
+      <c r="E47">
+        <v>154.02</v>
+      </c>
+      <c r="F47">
+        <v>258.12</v>
+      </c>
+      <c r="G47">
+        <v>31.7</v>
+      </c>
+      <c r="H47">
+        <v>469.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K47">
+        <v>2.67</v>
+      </c>
+      <c r="L47">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M47">
+        <v>61.639056</v>
+      </c>
+      <c r="N47">
+        <v>-70.99238933333334</v>
+      </c>
+      <c r="O47">
+        <v>-17.74809733333333</v>
+      </c>
+      <c r="P47">
+        <v>-53.244292</v>
+      </c>
+      <c r="Q47">
+        <v>-50.574292</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1507575008575515</v>
+      </c>
+      <c r="T47">
+        <v>1.516083176854735</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.03793590436124351</v>
+      </c>
+      <c r="W47">
+        <v>0.247859093961465</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.151743617444974</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1964532177543126</v>
+      </c>
+      <c r="C48">
+        <v>-24.19969692115623</v>
+      </c>
+      <c r="D48">
+        <v>207.9563030788438</v>
+      </c>
+      <c r="E48">
+        <v>159.756</v>
+      </c>
+      <c r="F48">
+        <v>263.856</v>
+      </c>
+      <c r="G48">
+        <v>31.7</v>
+      </c>
+      <c r="H48">
+        <v>469.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K48">
+        <v>2.67</v>
+      </c>
+      <c r="L48">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M48">
+        <v>63.0088128</v>
+      </c>
+      <c r="N48">
+        <v>-72.36214613333334</v>
+      </c>
+      <c r="O48">
+        <v>-18.09053653333334</v>
+      </c>
+      <c r="P48">
+        <v>-54.27160960000001</v>
+      </c>
+      <c r="Q48">
+        <v>-51.6016096</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1528307879104692</v>
+      </c>
+      <c r="T48">
+        <v>1.544158791240934</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.037111210788173</v>
+      </c>
+      <c r="W48">
+        <v>0.2476621571362157</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1484448431526921</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1984532177543126</v>
+      </c>
+      <c r="C49">
+        <v>-32.54079697493498</v>
+      </c>
+      <c r="D49">
+        <v>205.3512030250651</v>
+      </c>
+      <c r="E49">
+        <v>165.492</v>
+      </c>
+      <c r="F49">
+        <v>269.592</v>
+      </c>
+      <c r="G49">
+        <v>31.7</v>
+      </c>
+      <c r="H49">
+        <v>469.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K49">
+        <v>2.67</v>
+      </c>
+      <c r="L49">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M49">
+        <v>64.37856960000002</v>
+      </c>
+      <c r="N49">
+        <v>-73.73190293333336</v>
+      </c>
+      <c r="O49">
+        <v>-18.43297573333334</v>
+      </c>
+      <c r="P49">
+        <v>-55.29892720000002</v>
+      </c>
+      <c r="Q49">
+        <v>-52.62892720000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1549823122106667</v>
+      </c>
+      <c r="T49">
+        <v>1.573293862773782</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.0363216105586374</v>
+      </c>
+      <c r="W49">
+        <v>0.2474736006014026</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1452864422345497</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2004532177543126</v>
+      </c>
+      <c r="C50">
+        <v>-40.81743558241578</v>
+      </c>
+      <c r="D50">
+        <v>202.8105644175842</v>
+      </c>
+      <c r="E50">
+        <v>171.228</v>
+      </c>
+      <c r="F50">
+        <v>275.328</v>
+      </c>
+      <c r="G50">
+        <v>31.7</v>
+      </c>
+      <c r="H50">
+        <v>469.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K50">
+        <v>2.67</v>
+      </c>
+      <c r="L50">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M50">
+        <v>65.7483264</v>
+      </c>
+      <c r="N50">
+        <v>-75.10165973333334</v>
+      </c>
+      <c r="O50">
+        <v>-18.77541493333333</v>
+      </c>
+      <c r="P50">
+        <v>-56.3262448</v>
+      </c>
+      <c r="Q50">
+        <v>-53.6562448</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1572165874454872</v>
+      </c>
+      <c r="T50">
+        <v>1.60354951398097</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.0355649103386658</v>
+      </c>
+      <c r="W50">
+        <v>0.2472929005888734</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.1422596413546633</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2024532177543126</v>
+      </c>
+      <c r="C51">
+        <v>-49.0319760865452</v>
+      </c>
+      <c r="D51">
+        <v>200.3320239134548</v>
+      </c>
+      <c r="E51">
+        <v>176.964</v>
+      </c>
+      <c r="F51">
+        <v>281.064</v>
+      </c>
+      <c r="G51">
+        <v>31.7</v>
+      </c>
+      <c r="H51">
+        <v>469.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K51">
+        <v>2.67</v>
+      </c>
+      <c r="L51">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M51">
+        <v>67.11808320000002</v>
+      </c>
+      <c r="N51">
+        <v>-76.47141653333335</v>
+      </c>
+      <c r="O51">
+        <v>-19.11785413333334</v>
+      </c>
+      <c r="P51">
+        <v>-57.35356240000002</v>
+      </c>
+      <c r="Q51">
+        <v>-54.68356240000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1595384813169674</v>
+      </c>
+      <c r="T51">
+        <v>1.63499166131393</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.03483909584195832</v>
+      </c>
+      <c r="W51">
+        <v>0.2471195760870596</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.1393563833678333</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2044532177543126</v>
+      </c>
+      <c r="C52">
+        <v>-57.1866676957909</v>
+      </c>
+      <c r="D52">
+        <v>197.9133323042091</v>
+      </c>
+      <c r="E52">
+        <v>182.7</v>
+      </c>
+      <c r="F52">
+        <v>286.8</v>
+      </c>
+      <c r="G52">
+        <v>31.7</v>
+      </c>
+      <c r="H52">
+        <v>469.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K52">
+        <v>2.67</v>
+      </c>
+      <c r="L52">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M52">
+        <v>68.48784000000001</v>
+      </c>
+      <c r="N52">
+        <v>-77.84117333333334</v>
+      </c>
+      <c r="O52">
+        <v>-19.46029333333334</v>
+      </c>
+      <c r="P52">
+        <v>-58.38088</v>
+      </c>
+      <c r="Q52">
+        <v>-55.71088</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1619532509433067</v>
+      </c>
+      <c r="T52">
+        <v>1.667691494540209</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.03414231392511916</v>
+      </c>
+      <c r="W52">
+        <v>0.2469531845653185</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1365692557004767</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2064532177543126</v>
+      </c>
+      <c r="C53">
+        <v>-65.28365229191408</v>
+      </c>
+      <c r="D53">
+        <v>195.5523477080859</v>
+      </c>
+      <c r="E53">
+        <v>188.436</v>
+      </c>
+      <c r="F53">
+        <v>292.536</v>
+      </c>
+      <c r="G53">
+        <v>31.7</v>
+      </c>
+      <c r="H53">
+        <v>469.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K53">
+        <v>2.67</v>
+      </c>
+      <c r="L53">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M53">
+        <v>69.85759680000001</v>
+      </c>
+      <c r="N53">
+        <v>-79.21093013333335</v>
+      </c>
+      <c r="O53">
+        <v>-19.80273253333334</v>
+      </c>
+      <c r="P53">
+        <v>-59.40819760000001</v>
+      </c>
+      <c r="Q53">
+        <v>-56.73819760000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1644665825952109</v>
+      </c>
+      <c r="T53">
+        <v>1.701726014836948</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.03347285678933251</v>
+      </c>
+      <c r="W53">
+        <v>0.2467933182012926</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.1338914271573302</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2084532177543126</v>
+      </c>
+      <c r="C54">
+        <v>-73.32497075620967</v>
+      </c>
+      <c r="D54">
+        <v>193.2470292437904</v>
+      </c>
+      <c r="E54">
+        <v>194.1720000000001</v>
+      </c>
+      <c r="F54">
+        <v>298.272</v>
+      </c>
+      <c r="G54">
+        <v>31.7</v>
+      </c>
+      <c r="H54">
+        <v>469.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K54">
+        <v>2.67</v>
+      </c>
+      <c r="L54">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M54">
+        <v>71.22735360000001</v>
+      </c>
+      <c r="N54">
+        <v>-80.58068693333335</v>
+      </c>
+      <c r="O54">
+        <v>-20.14517173333334</v>
+      </c>
+      <c r="P54">
+        <v>-60.43551520000001</v>
+      </c>
+      <c r="Q54">
+        <v>-57.76551520000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1670846363992778</v>
+      </c>
+      <c r="T54">
+        <v>1.737178640146051</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.03282914800492227</v>
+      </c>
+      <c r="W54">
+        <v>0.2466396005435754</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.131316592019689</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2104532177543126</v>
+      </c>
+      <c r="C55">
+        <v>-81.31256885348958</v>
+      </c>
+      <c r="D55">
+        <v>190.9954311465105</v>
+      </c>
+      <c r="E55">
+        <v>199.908</v>
+      </c>
+      <c r="F55">
+        <v>304.008</v>
+      </c>
+      <c r="G55">
+        <v>31.7</v>
+      </c>
+      <c r="H55">
+        <v>469.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K55">
+        <v>2.67</v>
+      </c>
+      <c r="L55">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M55">
+        <v>72.59711040000002</v>
+      </c>
+      <c r="N55">
+        <v>-81.95044373333336</v>
+      </c>
+      <c r="O55">
+        <v>-20.48761093333334</v>
+      </c>
+      <c r="P55">
+        <v>-61.46283280000002</v>
+      </c>
+      <c r="Q55">
+        <v>-58.79283280000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1698140967481986</v>
+      </c>
+      <c r="T55">
+        <v>1.774139887808733</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.03220973011803694</v>
+      </c>
+      <c r="W55">
+        <v>0.2464916835521872</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.1288389204721478</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2124532177543126</v>
+      </c>
+      <c r="C56">
+        <v>-89.24830270946379</v>
+      </c>
+      <c r="D56">
+        <v>188.7956972905363</v>
+      </c>
+      <c r="E56">
+        <v>205.644</v>
+      </c>
+      <c r="F56">
+        <v>309.744</v>
+      </c>
+      <c r="G56">
+        <v>31.7</v>
+      </c>
+      <c r="H56">
+        <v>469.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K56">
+        <v>2.67</v>
+      </c>
+      <c r="L56">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M56">
+        <v>73.96686720000001</v>
+      </c>
+      <c r="N56">
+        <v>-83.32020053333335</v>
+      </c>
+      <c r="O56">
+        <v>-20.83005013333334</v>
+      </c>
+      <c r="P56">
+        <v>-62.49015040000001</v>
+      </c>
+      <c r="Q56">
+        <v>-59.82015040000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.172662229286203</v>
+      </c>
+      <c r="T56">
+        <v>1.812708146239357</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.03161325363436959</v>
+      </c>
+      <c r="W56">
+        <v>0.2463492449678875</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.1264530145374785</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2144532177543126</v>
+      </c>
+      <c r="C57">
+        <v>-97.13394391392612</v>
+      </c>
+      <c r="D57">
+        <v>186.6460560860739</v>
+      </c>
+      <c r="E57">
+        <v>211.38</v>
+      </c>
+      <c r="F57">
+        <v>315.48</v>
+      </c>
+      <c r="G57">
+        <v>31.7</v>
+      </c>
+      <c r="H57">
+        <v>469.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K57">
+        <v>2.67</v>
+      </c>
+      <c r="L57">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M57">
+        <v>75.33662400000001</v>
+      </c>
+      <c r="N57">
+        <v>-84.68995733333335</v>
+      </c>
+      <c r="O57">
+        <v>-21.17248933333334</v>
+      </c>
+      <c r="P57">
+        <v>-63.51746800000002</v>
+      </c>
+      <c r="Q57">
+        <v>-60.84746800000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.175636945492563</v>
+      </c>
+      <c r="T57">
+        <v>1.852990549489121</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.03103846720465378</v>
+      </c>
+      <c r="W57">
+        <v>0.2462119859684713</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.1241538688186152</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2164532177543126</v>
+      </c>
+      <c r="C58">
+        <v>-104.9711842792338</v>
+      </c>
+      <c r="D58">
+        <v>184.5448157207663</v>
+      </c>
+      <c r="E58">
+        <v>217.1160000000001</v>
+      </c>
+      <c r="F58">
+        <v>321.2160000000001</v>
+      </c>
+      <c r="G58">
+        <v>31.7</v>
+      </c>
+      <c r="H58">
+        <v>469.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K58">
+        <v>2.67</v>
+      </c>
+      <c r="L58">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M58">
+        <v>76.70638080000002</v>
+      </c>
+      <c r="N58">
+        <v>-86.05971413333336</v>
+      </c>
+      <c r="O58">
+        <v>-21.51492853333334</v>
+      </c>
+      <c r="P58">
+        <v>-64.54478560000001</v>
+      </c>
+      <c r="Q58">
+        <v>-61.87478560000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1787468760719394</v>
+      </c>
+      <c r="T58">
+        <v>1.895103971068419</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.03048420886171353</v>
+      </c>
+      <c r="W58">
+        <v>0.2460796290761772</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.1219368354468542</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2184532177543126</v>
+      </c>
+      <c r="C59">
+        <v>-112.7616402809419</v>
+      </c>
+      <c r="D59">
+        <v>182.4903597190581</v>
+      </c>
+      <c r="E59">
+        <v>222.8520000000001</v>
+      </c>
+      <c r="F59">
+        <v>326.9520000000001</v>
+      </c>
+      <c r="G59">
+        <v>31.7</v>
+      </c>
+      <c r="H59">
+        <v>469.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K59">
+        <v>2.67</v>
+      </c>
+      <c r="L59">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M59">
+        <v>78.07613760000002</v>
+      </c>
+      <c r="N59">
+        <v>-87.42947093333336</v>
+      </c>
+      <c r="O59">
+        <v>-21.85736773333334</v>
+      </c>
+      <c r="P59">
+        <v>-65.57210320000002</v>
+      </c>
+      <c r="Q59">
+        <v>-62.90210320000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1820014545852404</v>
+      </c>
+      <c r="T59">
+        <v>1.939176156442104</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.02994939817992908</v>
+      </c>
+      <c r="W59">
+        <v>0.2459519162853671</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.1197975927197164</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2204532177543126</v>
+      </c>
+      <c r="C60">
+        <v>-120.506857205091</v>
+      </c>
+      <c r="D60">
+        <v>180.481142794909</v>
+      </c>
+      <c r="E60">
+        <v>228.588</v>
+      </c>
+      <c r="F60">
+        <v>332.688</v>
+      </c>
+      <c r="G60">
+        <v>31.7</v>
+      </c>
+      <c r="H60">
+        <v>469.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K60">
+        <v>2.67</v>
+      </c>
+      <c r="L60">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M60">
+        <v>79.4458944</v>
+      </c>
+      <c r="N60">
+        <v>-88.79922773333334</v>
+      </c>
+      <c r="O60">
+        <v>-22.19980693333333</v>
+      </c>
+      <c r="P60">
+        <v>-66.5994208</v>
+      </c>
+      <c r="Q60">
+        <v>-63.9294208</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1854110130277461</v>
+      </c>
+      <c r="T60">
+        <v>1.985347017309772</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.02943302924579238</v>
+      </c>
+      <c r="W60">
+        <v>0.2458286073838952</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.1177321169831695</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2224532177543126</v>
+      </c>
+      <c r="C61">
+        <v>-128.2083130245078</v>
+      </c>
+      <c r="D61">
+        <v>178.5156869754922</v>
+      </c>
+      <c r="E61">
+        <v>234.324</v>
+      </c>
+      <c r="F61">
+        <v>338.424</v>
+      </c>
+      <c r="G61">
+        <v>31.7</v>
+      </c>
+      <c r="H61">
+        <v>469.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K61">
+        <v>2.67</v>
+      </c>
+      <c r="L61">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M61">
+        <v>80.8156512</v>
+      </c>
+      <c r="N61">
+        <v>-90.16898453333334</v>
+      </c>
+      <c r="O61">
+        <v>-22.54224613333334</v>
+      </c>
+      <c r="P61">
+        <v>-67.62673840000001</v>
+      </c>
+      <c r="Q61">
+        <v>-64.95673840000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1889868913942764</v>
+      </c>
+      <c r="T61">
+        <v>2.033770115292937</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.02893416434332132</v>
+      </c>
+      <c r="W61">
+        <v>0.2457094784451852</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1157366573732854</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2244532177543126</v>
+      </c>
+      <c r="C62">
+        <v>-135.8674220245547</v>
+      </c>
+      <c r="D62">
+        <v>176.5925779754454</v>
+      </c>
+      <c r="E62">
+        <v>240.06</v>
+      </c>
+      <c r="F62">
+        <v>344.16</v>
+      </c>
+      <c r="G62">
+        <v>31.7</v>
+      </c>
+      <c r="H62">
+        <v>469.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K62">
+        <v>2.67</v>
+      </c>
+      <c r="L62">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M62">
+        <v>82.18540800000001</v>
+      </c>
+      <c r="N62">
+        <v>-91.53874133333335</v>
+      </c>
+      <c r="O62">
+        <v>-22.88468533333334</v>
+      </c>
+      <c r="P62">
+        <v>-68.65405600000001</v>
+      </c>
+      <c r="Q62">
+        <v>-65.98405600000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1927415636791334</v>
+      </c>
+      <c r="T62">
+        <v>2.084614368175261</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.02845192827093264</v>
+      </c>
+      <c r="W62">
+        <v>0.2455943204710987</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.1138077130837305</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2264532177543126</v>
+      </c>
+      <c r="C63">
+        <v>-143.4855381970218</v>
+      </c>
+      <c r="D63">
+        <v>174.7104618029782</v>
+      </c>
+      <c r="E63">
+        <v>245.796</v>
+      </c>
+      <c r="F63">
+        <v>349.896</v>
+      </c>
+      <c r="G63">
+        <v>31.7</v>
+      </c>
+      <c r="H63">
+        <v>469.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K63">
+        <v>2.67</v>
+      </c>
+      <c r="L63">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M63">
+        <v>83.55516480000001</v>
+      </c>
+      <c r="N63">
+        <v>-92.90849813333335</v>
+      </c>
+      <c r="O63">
+        <v>-23.22712453333334</v>
+      </c>
+      <c r="P63">
+        <v>-69.68137360000001</v>
+      </c>
+      <c r="Q63">
+        <v>-67.01137360000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1966887832606496</v>
+      </c>
+      <c r="T63">
+        <v>2.138066018641294</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.02798550321731079</v>
+      </c>
+      <c r="W63">
+        <v>0.2454829381682938</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.1119420128692432</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2284532177543126</v>
+      </c>
+      <c r="C64">
+        <v>-151.0639584192751</v>
+      </c>
+      <c r="D64">
+        <v>172.8680415807249</v>
+      </c>
+      <c r="E64">
+        <v>251.532</v>
+      </c>
+      <c r="F64">
+        <v>355.632</v>
+      </c>
+      <c r="G64">
+        <v>31.7</v>
+      </c>
+      <c r="H64">
+        <v>469.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K64">
+        <v>2.67</v>
+      </c>
+      <c r="L64">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M64">
+        <v>84.9249216</v>
+      </c>
+      <c r="N64">
+        <v>-94.27825493333334</v>
+      </c>
+      <c r="O64">
+        <v>-23.56956373333334</v>
+      </c>
+      <c r="P64">
+        <v>-70.7086912</v>
+      </c>
+      <c r="Q64">
+        <v>-68.0386912</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2008437512411931</v>
+      </c>
+      <c r="T64">
+        <v>2.194330913868696</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.02753412413316061</v>
+      </c>
+      <c r="W64">
+        <v>0.2453751488429988</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1101364965326426</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2304532177543126</v>
+      </c>
+      <c r="C65">
+        <v>-158.6039254343485</v>
+      </c>
+      <c r="D65">
+        <v>171.0640745656515</v>
+      </c>
+      <c r="E65">
+        <v>257.268</v>
+      </c>
+      <c r="F65">
+        <v>361.368</v>
+      </c>
+      <c r="G65">
+        <v>31.7</v>
+      </c>
+      <c r="H65">
+        <v>469.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K65">
+        <v>2.67</v>
+      </c>
+      <c r="L65">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M65">
+        <v>86.29467840000001</v>
+      </c>
+      <c r="N65">
+        <v>-95.64801173333335</v>
+      </c>
+      <c r="O65">
+        <v>-23.91200293333334</v>
+      </c>
+      <c r="P65">
+        <v>-71.73600880000001</v>
+      </c>
+      <c r="Q65">
+        <v>-69.06600880000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2052233120855496</v>
+      </c>
+      <c r="T65">
+        <v>2.253637154784066</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.02709707454374537</v>
+      </c>
+      <c r="W65">
+        <v>0.2452707814010464</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.1083882981749815</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2324532177543126</v>
+      </c>
+      <c r="C66">
+        <v>-166.1066306463701</v>
+      </c>
+      <c r="D66">
+        <v>169.2973693536299</v>
+      </c>
+      <c r="E66">
+        <v>263.004</v>
+      </c>
+      <c r="F66">
+        <v>367.104</v>
+      </c>
+      <c r="G66">
+        <v>31.7</v>
+      </c>
+      <c r="H66">
+        <v>469.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K66">
+        <v>2.67</v>
+      </c>
+      <c r="L66">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M66">
+        <v>87.66443520000001</v>
+      </c>
+      <c r="N66">
+        <v>-97.01776853333335</v>
+      </c>
+      <c r="O66">
+        <v>-24.25444213333334</v>
+      </c>
+      <c r="P66">
+        <v>-72.76332640000001</v>
+      </c>
+      <c r="Q66">
+        <v>-70.09332640000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2098461818657038</v>
+      </c>
+      <c r="T66">
+        <v>2.316238186861401</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.02667368275399934</v>
+      </c>
+      <c r="W66">
+        <v>0.245169675441655</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.1066947310159974</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2344532177543126</v>
+      </c>
+      <c r="C67">
+        <v>-173.5732167445371</v>
+      </c>
+      <c r="D67">
+        <v>167.5667832554629</v>
+      </c>
+      <c r="E67">
+        <v>268.74</v>
+      </c>
+      <c r="F67">
+        <v>372.84</v>
+      </c>
+      <c r="G67">
+        <v>31.7</v>
+      </c>
+      <c r="H67">
+        <v>469.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K67">
+        <v>2.67</v>
+      </c>
+      <c r="L67">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M67">
+        <v>89.03419200000002</v>
+      </c>
+      <c r="N67">
+        <v>-98.38752533333336</v>
+      </c>
+      <c r="O67">
+        <v>-24.59688133333334</v>
+      </c>
+      <c r="P67">
+        <v>-73.79064400000001</v>
+      </c>
+      <c r="Q67">
+        <v>-71.12064400000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2147332156332953</v>
+      </c>
+      <c r="T67">
+        <v>2.382416420771727</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.02626331840393781</v>
+      </c>
+      <c r="W67">
+        <v>0.2450716804348604</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.1050532736157512</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2364532177543126</v>
+      </c>
+      <c r="C68">
+        <v>-181.0047801677823</v>
+      </c>
+      <c r="D68">
+        <v>165.8712198322177</v>
+      </c>
+      <c r="E68">
+        <v>274.476</v>
+      </c>
+      <c r="F68">
+        <v>378.576</v>
+      </c>
+      <c r="G68">
+        <v>31.7</v>
+      </c>
+      <c r="H68">
+        <v>469.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K68">
+        <v>2.67</v>
+      </c>
+      <c r="L68">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M68">
+        <v>90.40394880000001</v>
+      </c>
+      <c r="N68">
+        <v>-99.75728213333335</v>
+      </c>
+      <c r="O68">
+        <v>-24.93932053333334</v>
+      </c>
+      <c r="P68">
+        <v>-74.81796160000002</v>
+      </c>
+      <c r="Q68">
+        <v>-72.14796160000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2199077219754511</v>
+      </c>
+      <c r="T68">
+        <v>2.452487491970895</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.02586538933721149</v>
+      </c>
+      <c r="W68">
+        <v>0.2449766549737261</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.103461557348846</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2384532177543126</v>
+      </c>
+      <c r="C69">
+        <v>-188.4023734213038</v>
+      </c>
+      <c r="D69">
+        <v>164.2096265786962</v>
+      </c>
+      <c r="E69">
+        <v>280.212</v>
+      </c>
+      <c r="F69">
+        <v>384.312</v>
+      </c>
+      <c r="G69">
+        <v>31.7</v>
+      </c>
+      <c r="H69">
+        <v>469.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K69">
+        <v>2.67</v>
+      </c>
+      <c r="L69">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M69">
+        <v>91.77370560000001</v>
+      </c>
+      <c r="N69">
+        <v>-101.1270389333334</v>
+      </c>
+      <c r="O69">
+        <v>-25.28175973333334</v>
+      </c>
+      <c r="P69">
+        <v>-75.84527920000002</v>
+      </c>
+      <c r="Q69">
+        <v>-73.17527920000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.225395834762586</v>
+      </c>
+      <c r="T69">
+        <v>2.526805294757892</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.02547933875008893</v>
+      </c>
+      <c r="W69">
+        <v>0.2448844660935212</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.1019173550003558</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2404532177543126</v>
+      </c>
+      <c r="C70">
+        <v>-195.7670072552431</v>
+      </c>
+      <c r="D70">
+        <v>162.5809927447569</v>
+      </c>
+      <c r="E70">
+        <v>285.9480000000001</v>
+      </c>
+      <c r="F70">
+        <v>390.0480000000001</v>
+      </c>
+      <c r="G70">
+        <v>31.7</v>
+      </c>
+      <c r="H70">
+        <v>469.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K70">
+        <v>2.67</v>
+      </c>
+      <c r="L70">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M70">
+        <v>93.14346240000002</v>
+      </c>
+      <c r="N70">
+        <v>-102.4967957333334</v>
+      </c>
+      <c r="O70">
+        <v>-25.62419893333334</v>
+      </c>
+      <c r="P70">
+        <v>-76.87259680000003</v>
+      </c>
+      <c r="Q70">
+        <v>-74.20259680000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2312269545989168</v>
+      </c>
+      <c r="T70">
+        <v>2.605767960219076</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.02510464259199938</v>
+      </c>
+      <c r="W70">
+        <v>0.2447949886509695</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1004185703679976</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2424532177543126</v>
+      </c>
+      <c r="C71">
+        <v>-203.0996527149863</v>
+      </c>
+      <c r="D71">
+        <v>160.9843472850138</v>
+      </c>
+      <c r="E71">
+        <v>291.6840000000001</v>
+      </c>
+      <c r="F71">
+        <v>395.784</v>
+      </c>
+      <c r="G71">
+        <v>31.7</v>
+      </c>
+      <c r="H71">
+        <v>469.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K71">
+        <v>2.67</v>
+      </c>
+      <c r="L71">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M71">
+        <v>94.51321920000002</v>
+      </c>
+      <c r="N71">
+        <v>-103.8665525333334</v>
+      </c>
+      <c r="O71">
+        <v>-25.96663813333334</v>
+      </c>
+      <c r="P71">
+        <v>-77.89991440000003</v>
+      </c>
+      <c r="Q71">
+        <v>-75.22991440000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2374342757150109</v>
+      </c>
+      <c r="T71">
+        <v>2.689824991193885</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.02474080719211533</v>
+      </c>
+      <c r="W71">
+        <v>0.2447081047574771</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.09896322876846142</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2444532177543126</v>
+      </c>
+      <c r="C72">
+        <v>-210.40124307183</v>
+      </c>
+      <c r="D72">
+        <v>159.4187569281701</v>
+      </c>
+      <c r="E72">
+        <v>297.4200000000001</v>
+      </c>
+      <c r="F72">
+        <v>401.52</v>
+      </c>
+      <c r="G72">
+        <v>31.7</v>
+      </c>
+      <c r="H72">
+        <v>469.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K72">
+        <v>2.67</v>
+      </c>
+      <c r="L72">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M72">
+        <v>95.88297600000001</v>
+      </c>
+      <c r="N72">
+        <v>-105.2363093333334</v>
+      </c>
+      <c r="O72">
+        <v>-26.30907733333334</v>
+      </c>
+      <c r="P72">
+        <v>-78.92723200000002</v>
+      </c>
+      <c r="Q72">
+        <v>-76.25723200000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2440554182388446</v>
+      </c>
+      <c r="T72">
+        <v>2.779485824233682</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.02438736708937083</v>
+      </c>
+      <c r="W72">
+        <v>0.2446237032609418</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.09754946835748335</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2464532177543126</v>
+      </c>
+      <c r="C73">
+        <v>-217.6726756420758</v>
+      </c>
+      <c r="D73">
+        <v>157.8833243579242</v>
+      </c>
+      <c r="E73">
+        <v>303.1559999999999</v>
+      </c>
+      <c r="F73">
+        <v>407.256</v>
+      </c>
+      <c r="G73">
+        <v>31.7</v>
+      </c>
+      <c r="H73">
+        <v>469.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K73">
+        <v>2.67</v>
+      </c>
+      <c r="L73">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M73">
+        <v>97.2527328</v>
+      </c>
+      <c r="N73">
+        <v>-106.6060661333333</v>
+      </c>
+      <c r="O73">
+        <v>-26.65151653333334</v>
+      </c>
+      <c r="P73">
+        <v>-79.95454960000001</v>
+      </c>
+      <c r="Q73">
+        <v>-77.28454960000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2511331912815633</v>
+      </c>
+      <c r="T73">
+        <v>2.875330163000359</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.02404388304585857</v>
+      </c>
+      <c r="W73">
+        <v>0.244541679271351</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.09617553218343433</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2484532177543126</v>
+      </c>
+      <c r="C74">
+        <v>-224.9148135020056</v>
+      </c>
+      <c r="D74">
+        <v>156.3771864979944</v>
+      </c>
+      <c r="E74">
+        <v>308.8920000000001</v>
+      </c>
+      <c r="F74">
+        <v>412.992</v>
+      </c>
+      <c r="G74">
+        <v>31.7</v>
+      </c>
+      <c r="H74">
+        <v>469.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K74">
+        <v>2.67</v>
+      </c>
+      <c r="L74">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M74">
+        <v>98.62248960000001</v>
+      </c>
+      <c r="N74">
+        <v>-107.9758229333333</v>
+      </c>
+      <c r="O74">
+        <v>-26.99395573333334</v>
+      </c>
+      <c r="P74">
+        <v>-80.98186720000001</v>
+      </c>
+      <c r="Q74">
+        <v>-78.31186720000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2587165195416191</v>
+      </c>
+      <c r="T74">
+        <v>2.978020525964658</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.02370994022577719</v>
+      </c>
+      <c r="W74">
+        <v>0.2444619337259156</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.09483976090310886</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2504532177543126</v>
+      </c>
+      <c r="C75">
+        <v>-232.1284871056218</v>
+      </c>
+      <c r="D75">
+        <v>154.8995128943782</v>
+      </c>
+      <c r="E75">
+        <v>314.628</v>
+      </c>
+      <c r="F75">
+        <v>418.728</v>
+      </c>
+      <c r="G75">
+        <v>31.7</v>
+      </c>
+      <c r="H75">
+        <v>469.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K75">
+        <v>2.67</v>
+      </c>
+      <c r="L75">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M75">
+        <v>99.99224640000001</v>
+      </c>
+      <c r="N75">
+        <v>-109.3455797333334</v>
+      </c>
+      <c r="O75">
+        <v>-27.33639493333334</v>
+      </c>
+      <c r="P75">
+        <v>-82.00918480000001</v>
+      </c>
+      <c r="Q75">
+        <v>-79.33918480000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2668615758209383</v>
+      </c>
+      <c r="T75">
+        <v>3.088317582481868</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.02338514652405422</v>
+      </c>
+      <c r="W75">
+        <v>0.2443843729899442</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.09354058609621685</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2524532177543126</v>
+      </c>
+      <c r="C76">
+        <v>-239.3144958115286</v>
+      </c>
+      <c r="D76">
+        <v>153.4495041884714</v>
+      </c>
+      <c r="E76">
+        <v>320.364</v>
+      </c>
+      <c r="F76">
+        <v>424.464</v>
+      </c>
+      <c r="G76">
+        <v>31.7</v>
+      </c>
+      <c r="H76">
+        <v>469.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K76">
+        <v>2.67</v>
+      </c>
+      <c r="L76">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M76">
+        <v>101.3620032</v>
+      </c>
+      <c r="N76">
+        <v>-110.7153365333333</v>
+      </c>
+      <c r="O76">
+        <v>-27.67883413333334</v>
+      </c>
+      <c r="P76">
+        <v>-83.0365024</v>
+      </c>
+      <c r="Q76">
+        <v>-80.3665024</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2756331748909744</v>
+      </c>
+      <c r="T76">
+        <v>3.20709902796194</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.02306913103048592</v>
+      </c>
+      <c r="W76">
+        <v>0.2443089084900801</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.09227652412194365</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2544532177543126</v>
+      </c>
+      <c r="C77">
+        <v>-246.4736093248478</v>
+      </c>
+      <c r="D77">
+        <v>152.0263906751522</v>
+      </c>
+      <c r="E77">
+        <v>326.1</v>
+      </c>
+      <c r="F77">
+        <v>430.2</v>
+      </c>
+      <c r="G77">
+        <v>31.7</v>
+      </c>
+      <c r="H77">
+        <v>469.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K77">
+        <v>2.67</v>
+      </c>
+      <c r="L77">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M77">
+        <v>102.73176</v>
+      </c>
+      <c r="N77">
+        <v>-112.0850933333334</v>
+      </c>
+      <c r="O77">
+        <v>-28.02127333333334</v>
+      </c>
+      <c r="P77">
+        <v>-84.06382000000002</v>
+      </c>
+      <c r="Q77">
+        <v>-81.39382000000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2851065018866134</v>
+      </c>
+      <c r="T77">
+        <v>3.335382989080417</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.0227615426167461</v>
+      </c>
+      <c r="W77">
+        <v>0.244235456376879</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.09104617046698449</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2564532177543126</v>
+      </c>
+      <c r="C78">
+        <v>-253.606569059638</v>
+      </c>
+      <c r="D78">
+        <v>150.629430940362</v>
+      </c>
+      <c r="E78">
+        <v>331.836</v>
+      </c>
+      <c r="F78">
+        <v>435.936</v>
+      </c>
+      <c r="G78">
+        <v>31.7</v>
+      </c>
+      <c r="H78">
+        <v>469.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K78">
+        <v>2.67</v>
+      </c>
+      <c r="L78">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M78">
+        <v>104.1015168</v>
+      </c>
+      <c r="N78">
+        <v>-113.4548501333334</v>
+      </c>
+      <c r="O78">
+        <v>-28.36371253333334</v>
+      </c>
+      <c r="P78">
+        <v>-85.09113760000001</v>
+      </c>
+      <c r="Q78">
+        <v>-82.42113760000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2953692727985556</v>
+      </c>
+      <c r="T78">
+        <v>3.474357280292101</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.02246204863494682</v>
+      </c>
+      <c r="W78">
+        <v>0.2441639372140253</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.08984819453978732</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2584532177543126</v>
+      </c>
+      <c r="C79">
+        <v>-260.7140894268821</v>
+      </c>
+      <c r="D79">
+        <v>149.2579105731179</v>
+      </c>
+      <c r="E79">
+        <v>337.572</v>
+      </c>
+      <c r="F79">
+        <v>441.672</v>
+      </c>
+      <c r="G79">
+        <v>31.7</v>
+      </c>
+      <c r="H79">
+        <v>469.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K79">
+        <v>2.67</v>
+      </c>
+      <c r="L79">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M79">
+        <v>105.4712736</v>
+      </c>
+      <c r="N79">
+        <v>-114.8246069333334</v>
+      </c>
+      <c r="O79">
+        <v>-28.70615173333334</v>
+      </c>
+      <c r="P79">
+        <v>-86.11845520000001</v>
+      </c>
+      <c r="Q79">
+        <v>-83.44845520000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3065244585724059</v>
+      </c>
+      <c r="T79">
+        <v>3.625416292478715</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.02217033371760984</v>
+      </c>
+      <c r="W79">
+        <v>0.2440942756917652</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.08868133487043939</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2604532177543126</v>
+      </c>
+      <c r="C80">
+        <v>-267.7968590527448</v>
+      </c>
+      <c r="D80">
+        <v>147.9111409472552</v>
+      </c>
+      <c r="E80">
+        <v>343.308</v>
+      </c>
+      <c r="F80">
+        <v>447.408</v>
+      </c>
+      <c r="G80">
+        <v>31.7</v>
+      </c>
+      <c r="H80">
+        <v>469.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K80">
+        <v>2.67</v>
+      </c>
+      <c r="L80">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M80">
+        <v>106.8410304</v>
+      </c>
+      <c r="N80">
+        <v>-116.1943637333333</v>
+      </c>
+      <c r="O80">
+        <v>-29.04859093333334</v>
+      </c>
+      <c r="P80">
+        <v>-87.1457728</v>
+      </c>
+      <c r="Q80">
+        <v>-84.4757728</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.318693752143879</v>
+      </c>
+      <c r="T80">
+        <v>3.790207942136839</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.02188609866994818</v>
+      </c>
+      <c r="W80">
+        <v>0.2440264003623837</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.08754439467979269</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2624532177543126</v>
+      </c>
+      <c r="C81">
+        <v>-274.855541931466</v>
+      </c>
+      <c r="D81">
+        <v>146.5884580685342</v>
+      </c>
+      <c r="E81">
+        <v>349.0440000000001</v>
+      </c>
+      <c r="F81">
+        <v>453.1440000000001</v>
+      </c>
+      <c r="G81">
+        <v>31.7</v>
+      </c>
+      <c r="H81">
+        <v>469.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K81">
+        <v>2.67</v>
+      </c>
+      <c r="L81">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M81">
+        <v>108.2107872</v>
+      </c>
+      <c r="N81">
+        <v>-117.5641205333334</v>
+      </c>
+      <c r="O81">
+        <v>-29.39103013333334</v>
+      </c>
+      <c r="P81">
+        <v>-88.17309040000002</v>
+      </c>
+      <c r="Q81">
+        <v>-85.50309040000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3320220260554922</v>
+      </c>
+      <c r="T81">
+        <v>3.970694034619545</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.02160905944627795</v>
+      </c>
+      <c r="W81">
+        <v>0.2439602433957712</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.08643623778511178</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2644532177543126</v>
+      </c>
+      <c r="C82">
+        <v>-281.8907785169432</v>
+      </c>
+      <c r="D82">
+        <v>145.2892214830569</v>
+      </c>
+      <c r="E82">
+        <v>354.7800000000001</v>
+      </c>
+      <c r="F82">
+        <v>458.8800000000001</v>
+      </c>
+      <c r="G82">
+        <v>31.7</v>
+      </c>
+      <c r="H82">
+        <v>469.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K82">
+        <v>2.67</v>
+      </c>
+      <c r="L82">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M82">
+        <v>109.580544</v>
+      </c>
+      <c r="N82">
+        <v>-118.9338773333334</v>
+      </c>
+      <c r="O82">
+        <v>-29.73346933333334</v>
+      </c>
+      <c r="P82">
+        <v>-89.20040800000001</v>
+      </c>
+      <c r="Q82">
+        <v>-86.53040800000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3466831273582668</v>
+      </c>
+      <c r="T82">
+        <v>4.169228736350522</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.02133894620319948</v>
+      </c>
+      <c r="W82">
+        <v>0.243895740353324</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.08535578481279793</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2664532177543126</v>
+      </c>
+      <c r="C83">
+        <v>-288.9031867567762</v>
+      </c>
+      <c r="D83">
+        <v>144.0128132432239</v>
+      </c>
+      <c r="E83">
+        <v>360.5160000000001</v>
+      </c>
+      <c r="F83">
+        <v>464.616</v>
+      </c>
+      <c r="G83">
+        <v>31.7</v>
+      </c>
+      <c r="H83">
+        <v>469.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K83">
+        <v>2.67</v>
+      </c>
+      <c r="L83">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M83">
+        <v>110.9503008</v>
+      </c>
+      <c r="N83">
+        <v>-120.3036341333334</v>
+      </c>
+      <c r="O83">
+        <v>-30.07590853333334</v>
+      </c>
+      <c r="P83">
+        <v>-90.22772560000001</v>
+      </c>
+      <c r="Q83">
+        <v>-87.55772560000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3628875024823862</v>
+      </c>
+      <c r="T83">
+        <v>4.388661827737392</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.02107550242291306</v>
+      </c>
+      <c r="W83">
+        <v>0.2438328299785916</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.08430200969165225</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2684532177543126</v>
+      </c>
+      <c r="C84">
+        <v>-295.893363072279</v>
+      </c>
+      <c r="D84">
+        <v>142.7586369277211</v>
+      </c>
+      <c r="E84">
+        <v>366.2520000000001</v>
+      </c>
+      <c r="F84">
+        <v>470.352</v>
+      </c>
+      <c r="G84">
+        <v>31.7</v>
+      </c>
+      <c r="H84">
+        <v>469.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K84">
+        <v>2.67</v>
+      </c>
+      <c r="L84">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M84">
+        <v>112.3200576</v>
+      </c>
+      <c r="N84">
+        <v>-121.6733909333334</v>
+      </c>
+      <c r="O84">
+        <v>-30.41834773333334</v>
+      </c>
+      <c r="P84">
+        <v>-91.25504320000002</v>
+      </c>
+      <c r="Q84">
+        <v>-88.58504320000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3808923637314076</v>
+      </c>
+      <c r="T84">
+        <v>4.632476373722803</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.02081848410068242</v>
+      </c>
+      <c r="W84">
+        <v>0.243771454003243</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.08327393640272973</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2704532177543126</v>
+      </c>
+      <c r="C85">
+        <v>-302.8618832877256</v>
+      </c>
+      <c r="D85">
+        <v>141.5261167122745</v>
+      </c>
+      <c r="E85">
+        <v>371.9880000000001</v>
+      </c>
+      <c r="F85">
+        <v>476.0880000000001</v>
+      </c>
+      <c r="G85">
+        <v>31.7</v>
+      </c>
+      <c r="H85">
+        <v>469.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K85">
+        <v>2.67</v>
+      </c>
+      <c r="L85">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M85">
+        <v>113.6898144</v>
+      </c>
+      <c r="N85">
+        <v>-123.0431477333334</v>
+      </c>
+      <c r="O85">
+        <v>-30.76078693333334</v>
+      </c>
+      <c r="P85">
+        <v>-92.28236080000002</v>
+      </c>
+      <c r="Q85">
+        <v>-89.61236080000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4010154439509023</v>
+      </c>
+      <c r="T85">
+        <v>4.904974983941793</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.02056765899103563</v>
+      </c>
+      <c r="W85">
+        <v>0.2437115569670593</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.08227063596414252</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2724532177543126</v>
+      </c>
+      <c r="C86">
+        <v>-309.8093035118723</v>
+      </c>
+      <c r="D86">
+        <v>140.3146964881277</v>
+      </c>
+      <c r="E86">
+        <v>377.724</v>
+      </c>
+      <c r="F86">
+        <v>481.824</v>
+      </c>
+      <c r="G86">
+        <v>31.7</v>
+      </c>
+      <c r="H86">
+        <v>469.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K86">
+        <v>2.67</v>
+      </c>
+      <c r="L86">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M86">
+        <v>115.0595712</v>
+      </c>
+      <c r="N86">
+        <v>-124.4129045333333</v>
+      </c>
+      <c r="O86">
+        <v>-31.10322613333334</v>
+      </c>
+      <c r="P86">
+        <v>-93.30967840000001</v>
+      </c>
+      <c r="Q86">
+        <v>-90.63967840000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4236539091978335</v>
+      </c>
+      <c r="T86">
+        <v>5.211535920438152</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.02032280590780903</v>
+      </c>
+      <c r="W86">
+        <v>0.2436530860507848</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.0812912236312362</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2744532177543126</v>
+      </c>
+      <c r="C87">
+        <v>-316.7361609745903</v>
+      </c>
+      <c r="D87">
+        <v>139.1238390254097</v>
+      </c>
+      <c r="E87">
+        <v>383.46</v>
+      </c>
+      <c r="F87">
+        <v>487.56</v>
+      </c>
+      <c r="G87">
+        <v>31.7</v>
+      </c>
+      <c r="H87">
+        <v>469.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K87">
+        <v>2.67</v>
+      </c>
+      <c r="L87">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M87">
+        <v>116.429328</v>
+      </c>
+      <c r="N87">
+        <v>-125.7826613333334</v>
+      </c>
+      <c r="O87">
+        <v>-31.44566533333334</v>
+      </c>
+      <c r="P87">
+        <v>-94.33699600000001</v>
+      </c>
+      <c r="Q87">
+        <v>-91.66699600000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.449310836477689</v>
+      </c>
+      <c r="T87">
+        <v>5.558971648467362</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.02008371407359951</v>
+      </c>
+      <c r="W87">
+        <v>0.2435959909207756</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.08033485629439818</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2764532177543126</v>
+      </c>
+      <c r="C88">
+        <v>-323.6429748212536</v>
+      </c>
+      <c r="D88">
+        <v>137.9530251787464</v>
+      </c>
+      <c r="E88">
+        <v>389.196</v>
+      </c>
+      <c r="F88">
+        <v>493.296</v>
+      </c>
+      <c r="G88">
+        <v>31.7</v>
+      </c>
+      <c r="H88">
+        <v>469.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K88">
+        <v>2.67</v>
+      </c>
+      <c r="L88">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M88">
+        <v>117.7990848</v>
+      </c>
+      <c r="N88">
+        <v>-127.1524181333333</v>
+      </c>
+      <c r="O88">
+        <v>-31.78810453333334</v>
+      </c>
+      <c r="P88">
+        <v>-95.3643136</v>
+      </c>
+      <c r="Q88">
+        <v>-92.6943136</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4786330390832382</v>
+      </c>
+      <c r="T88">
+        <v>5.956041051929317</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.01985018251460417</v>
+      </c>
+      <c r="W88">
+        <v>0.2435402235844875</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.07940073005841675</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2784532177543126</v>
+      </c>
+      <c r="C89">
+        <v>-330.5302468673496</v>
+      </c>
+      <c r="D89">
+        <v>136.8017531326504</v>
+      </c>
+      <c r="E89">
+        <v>394.932</v>
+      </c>
+      <c r="F89">
+        <v>499.032</v>
+      </c>
+      <c r="G89">
+        <v>31.7</v>
+      </c>
+      <c r="H89">
+        <v>469.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K89">
+        <v>2.67</v>
+      </c>
+      <c r="L89">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M89">
+        <v>119.1688416</v>
+      </c>
+      <c r="N89">
+        <v>-128.5221749333334</v>
+      </c>
+      <c r="O89">
+        <v>-32.13054373333334</v>
+      </c>
+      <c r="P89">
+        <v>-96.39163120000002</v>
+      </c>
+      <c r="Q89">
+        <v>-93.72163120000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5124663497819488</v>
+      </c>
+      <c r="T89">
+        <v>6.41419805592388</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.01962201949719492</v>
+      </c>
+      <c r="W89">
+        <v>0.2434857382559302</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.07848807798877977</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2804532177543126</v>
+      </c>
+      <c r="C90">
+        <v>-337.3984623156184</v>
+      </c>
+      <c r="D90">
+        <v>135.6695376843816</v>
+      </c>
+      <c r="E90">
+        <v>400.668</v>
+      </c>
+      <c r="F90">
+        <v>504.768</v>
+      </c>
+      <c r="G90">
+        <v>31.7</v>
+      </c>
+      <c r="H90">
+        <v>469.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K90">
+        <v>2.67</v>
+      </c>
+      <c r="L90">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M90">
+        <v>120.5385984</v>
+      </c>
+      <c r="N90">
+        <v>-129.8919317333333</v>
+      </c>
+      <c r="O90">
+        <v>-32.47298293333333</v>
+      </c>
+      <c r="P90">
+        <v>-97.41894880000001</v>
+      </c>
+      <c r="Q90">
+        <v>-94.74894880000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5519385455971113</v>
+      </c>
+      <c r="T90">
+        <v>6.948714560584205</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.01939904200290862</v>
+      </c>
+      <c r="W90">
+        <v>0.2434324912302946</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.07759616801163438</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2824532177543126</v>
+      </c>
+      <c r="C91">
+        <v>-344.248090437872</v>
+      </c>
+      <c r="D91">
+        <v>134.5559095621281</v>
+      </c>
+      <c r="E91">
+        <v>406.404</v>
+      </c>
+      <c r="F91">
+        <v>510.504</v>
+      </c>
+      <c r="G91">
+        <v>31.7</v>
+      </c>
+      <c r="H91">
+        <v>469.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K91">
+        <v>2.67</v>
+      </c>
+      <c r="L91">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M91">
+        <v>121.9083552</v>
+      </c>
+      <c r="N91">
+        <v>-131.2616885333333</v>
+      </c>
+      <c r="O91">
+        <v>-32.81542213333334</v>
+      </c>
+      <c r="P91">
+        <v>-98.44626640000001</v>
+      </c>
+      <c r="Q91">
+        <v>-95.77626640000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5985875042877578</v>
+      </c>
+      <c r="T91">
+        <v>7.580415884273677</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.01918107523883099</v>
+      </c>
+      <c r="W91">
+        <v>0.2433804407670329</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.07672430095532379</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2844532177543126</v>
+      </c>
+      <c r="C92">
+        <v>-351.0795852235067</v>
+      </c>
+      <c r="D92">
+        <v>133.4604147764933</v>
+      </c>
+      <c r="E92">
+        <v>412.14</v>
+      </c>
+      <c r="F92">
+        <v>516.24</v>
+      </c>
+      <c r="G92">
+        <v>31.7</v>
+      </c>
+      <c r="H92">
+        <v>469.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K92">
+        <v>2.67</v>
+      </c>
+      <c r="L92">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M92">
+        <v>123.278112</v>
+      </c>
+      <c r="N92">
+        <v>-132.6314453333333</v>
+      </c>
+      <c r="O92">
+        <v>-33.15786133333334</v>
+      </c>
+      <c r="P92">
+        <v>-99.47358400000002</v>
+      </c>
+      <c r="Q92">
+        <v>-96.80358400000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6545662547165338</v>
+      </c>
+      <c r="T92">
+        <v>8.338457472701046</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.01896795218062176</v>
+      </c>
+      <c r="W92">
+        <v>0.2433295469807325</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.075871808722487</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2864532177543127</v>
+      </c>
+      <c r="C93">
+        <v>-357.8933859965933</v>
+      </c>
+      <c r="D93">
+        <v>132.3826140034067</v>
+      </c>
+      <c r="E93">
+        <v>417.876</v>
+      </c>
+      <c r="F93">
+        <v>521.976</v>
+      </c>
+      <c r="G93">
+        <v>31.7</v>
+      </c>
+      <c r="H93">
+        <v>469.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K93">
+        <v>2.67</v>
+      </c>
+      <c r="L93">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M93">
+        <v>124.6478688</v>
+      </c>
+      <c r="N93">
+        <v>-134.0012021333334</v>
+      </c>
+      <c r="O93">
+        <v>-33.50030053333334</v>
+      </c>
+      <c r="P93">
+        <v>-100.5009016</v>
+      </c>
+      <c r="Q93">
+        <v>-97.83090160000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7229847274628152</v>
+      </c>
+      <c r="T93">
+        <v>9.264952747445607</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.01875951314566987</v>
+      </c>
+      <c r="W93">
+        <v>0.243279771739186</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.07503805258267948</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2884532177543126</v>
+      </c>
+      <c r="C94">
+        <v>-364.6899180033042</v>
+      </c>
+      <c r="D94">
+        <v>131.3220819966958</v>
+      </c>
+      <c r="E94">
+        <v>423.612</v>
+      </c>
+      <c r="F94">
+        <v>527.712</v>
+      </c>
+      <c r="G94">
+        <v>31.7</v>
+      </c>
+      <c r="H94">
+        <v>469.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K94">
+        <v>2.67</v>
+      </c>
+      <c r="L94">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M94">
+        <v>126.0176256</v>
+      </c>
+      <c r="N94">
+        <v>-135.3709589333333</v>
+      </c>
+      <c r="O94">
+        <v>-33.84273973333333</v>
+      </c>
+      <c r="P94">
+        <v>-101.5282192</v>
+      </c>
+      <c r="Q94">
+        <v>-98.85821919999999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8085078183956673</v>
+      </c>
+      <c r="T94">
+        <v>10.42307184087631</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.0185556053940865</v>
+      </c>
+      <c r="W94">
+        <v>0.2432310785681079</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.07422242157634584</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2904532177543125</v>
+      </c>
+      <c r="C95">
+        <v>-371.4695929713304</v>
+      </c>
+      <c r="D95">
+        <v>130.2784070286698</v>
+      </c>
+      <c r="E95">
+        <v>429.3480000000001</v>
+      </c>
+      <c r="F95">
+        <v>533.4480000000001</v>
+      </c>
+      <c r="G95">
+        <v>31.7</v>
+      </c>
+      <c r="H95">
+        <v>469.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K95">
+        <v>2.67</v>
+      </c>
+      <c r="L95">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M95">
+        <v>127.3873824</v>
+      </c>
+      <c r="N95">
+        <v>-136.7407157333334</v>
+      </c>
+      <c r="O95">
+        <v>-34.18517893333334</v>
+      </c>
+      <c r="P95">
+        <v>-102.5555368</v>
+      </c>
+      <c r="Q95">
+        <v>-99.88553680000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9184660781664771</v>
+      </c>
+      <c r="T95">
+        <v>11.91208210385864</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.01835608275544041</v>
+      </c>
+      <c r="W95">
+        <v>0.2431834325619991</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.07342433102176149</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2924532177543127</v>
+      </c>
+      <c r="C96">
+        <v>-378.2328096428323</v>
+      </c>
+      <c r="D96">
+        <v>129.2511903571678</v>
+      </c>
+      <c r="E96">
+        <v>435.0840000000001</v>
+      </c>
+      <c r="F96">
+        <v>539.1840000000001</v>
+      </c>
+      <c r="G96">
+        <v>31.7</v>
+      </c>
+      <c r="H96">
+        <v>469.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K96">
+        <v>2.67</v>
+      </c>
+      <c r="L96">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M96">
+        <v>128.7571392</v>
+      </c>
+      <c r="N96">
+        <v>-138.1104725333334</v>
+      </c>
+      <c r="O96">
+        <v>-34.52761813333334</v>
+      </c>
+      <c r="P96">
+        <v>-103.5828544</v>
+      </c>
+      <c r="Q96">
+        <v>-100.9128544</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.065077091194224</v>
+      </c>
+      <c r="T96">
+        <v>13.89742912116842</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.0181608052793187</v>
+      </c>
+      <c r="W96">
+        <v>0.2431368003007013</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.07264322111727473</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2944532177543127</v>
+      </c>
+      <c r="C97">
+        <v>-384.9799542823758</v>
+      </c>
+      <c r="D97">
+        <v>128.2400457176242</v>
+      </c>
+      <c r="E97">
+        <v>440.8200000000001</v>
+      </c>
+      <c r="F97">
+        <v>544.9200000000001</v>
+      </c>
+      <c r="G97">
+        <v>31.7</v>
+      </c>
+      <c r="H97">
+        <v>469.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K97">
+        <v>2.67</v>
+      </c>
+      <c r="L97">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M97">
+        <v>130.126896</v>
+      </c>
+      <c r="N97">
+        <v>-139.4802293333333</v>
+      </c>
+      <c r="O97">
+        <v>-34.87005733333334</v>
+      </c>
+      <c r="P97">
+        <v>-104.610172</v>
+      </c>
+      <c r="Q97">
+        <v>-101.940172</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.270332509433069</v>
+      </c>
+      <c r="T97">
+        <v>16.67691494540211</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.01796963890795745</v>
+      </c>
+      <c r="W97">
+        <v>0.2430911497712203</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.07187855563182977</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2964532177543125</v>
+      </c>
+      <c r="C98">
+        <v>-391.7114011612104</v>
+      </c>
+      <c r="D98">
+        <v>127.2445988387896</v>
+      </c>
+      <c r="E98">
+        <v>446.5559999999999</v>
+      </c>
+      <c r="F98">
+        <v>550.6559999999999</v>
+      </c>
+      <c r="G98">
+        <v>31.7</v>
+      </c>
+      <c r="H98">
+        <v>469.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K98">
+        <v>2.67</v>
+      </c>
+      <c r="L98">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M98">
+        <v>131.4966528</v>
+      </c>
+      <c r="N98">
+        <v>-140.8499861333333</v>
+      </c>
+      <c r="O98">
+        <v>-35.21249653333333</v>
+      </c>
+      <c r="P98">
+        <v>-105.6374896</v>
+      </c>
+      <c r="Q98">
+        <v>-102.9674896</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.578215636791332</v>
+      </c>
+      <c r="T98">
+        <v>20.84614368175259</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.0177824551693329</v>
+      </c>
+      <c r="W98">
+        <v>0.2430464502944367</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.07112982067733142</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2984532177543126</v>
+      </c>
+      <c r="C99">
+        <v>-398.4275130191671</v>
+      </c>
+      <c r="D99">
+        <v>126.264486980833</v>
+      </c>
+      <c r="E99">
+        <v>452.292</v>
+      </c>
+      <c r="F99">
+        <v>556.3920000000001</v>
+      </c>
+      <c r="G99">
+        <v>31.7</v>
+      </c>
+      <c r="H99">
+        <v>469.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K99">
+        <v>2.67</v>
+      </c>
+      <c r="L99">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M99">
+        <v>132.8664096</v>
+      </c>
+      <c r="N99">
+        <v>-142.2197429333334</v>
+      </c>
+      <c r="O99">
+        <v>-35.55493573333334</v>
+      </c>
+      <c r="P99">
+        <v>-106.6648072</v>
+      </c>
+      <c r="Q99">
+        <v>-103.9948072</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.091354182388444</v>
+      </c>
+      <c r="T99">
+        <v>27.79485824233679</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.01759913088923668</v>
+      </c>
+      <c r="W99">
+        <v>0.2430026724563497</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.07039652355694659</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3004532177543126</v>
+      </c>
+      <c r="C100">
+        <v>-405.1286415053712</v>
+      </c>
+      <c r="D100">
+        <v>125.2993584946288</v>
+      </c>
+      <c r="E100">
+        <v>458.028</v>
+      </c>
+      <c r="F100">
+        <v>562.128</v>
+      </c>
+      <c r="G100">
+        <v>31.7</v>
+      </c>
+      <c r="H100">
+        <v>469.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K100">
+        <v>2.67</v>
+      </c>
+      <c r="L100">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M100">
+        <v>134.2361664</v>
+      </c>
+      <c r="N100">
+        <v>-143.5894997333334</v>
+      </c>
+      <c r="O100">
+        <v>-35.89737493333334</v>
+      </c>
+      <c r="P100">
+        <v>-107.6921248</v>
+      </c>
+      <c r="Q100">
+        <v>-105.0221248</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.117631273582665</v>
+      </c>
+      <c r="T100">
+        <v>41.69228736350518</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.01741954792097916</v>
+      </c>
+      <c r="W100">
+        <v>0.2429597880435298</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.06967819168391665</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3024532177543126</v>
+      </c>
+      <c r="C101">
+        <v>-411.8151275988988</v>
+      </c>
+      <c r="D101">
+        <v>124.3488724011013</v>
+      </c>
+      <c r="E101">
+        <v>463.764</v>
+      </c>
+      <c r="F101">
+        <v>567.864</v>
+      </c>
+      <c r="G101">
+        <v>31.7</v>
+      </c>
+      <c r="H101">
+        <v>469.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>-6.683333333333334</v>
+      </c>
+      <c r="K101">
+        <v>2.67</v>
+      </c>
+      <c r="L101">
+        <v>-9.353333333333333</v>
+      </c>
+      <c r="M101">
+        <v>135.6059232</v>
+      </c>
+      <c r="N101">
+        <v>-144.9592565333333</v>
+      </c>
+      <c r="O101">
+        <v>-36.23981413333333</v>
+      </c>
+      <c r="P101">
+        <v>-108.7194424</v>
+      </c>
+      <c r="Q101">
+        <v>-106.0494424</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.19646254716533</v>
+      </c>
+      <c r="T101">
+        <v>83.38457472701036</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.01724359289147432</v>
+      </c>
+      <c r="W101">
+        <v>0.2429177699824841</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.06897437156589725</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
